--- a/Next Plc-Three Statement Financial model.xlsx
+++ b/Next Plc-Three Statement Financial model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a0316d2243f45c1/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1189" documentId="14_{041815F9-8712-4039-80DC-A7C457710C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C76DBFCB-8550-452F-8E0B-A581E86B5C10}"/>
+  <xr:revisionPtr revIDLastSave="1191" documentId="14_{041815F9-8712-4039-80DC-A7C457710C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A07E0151-7185-4178-A9A1-532DA6C7259D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FAF94146-EDEE-409D-AB60-D72469E73829}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{FAF94146-EDEE-409D-AB60-D72469E73829}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="1" r:id="rId1"/>
@@ -2298,9 +2298,6 @@
     <t>Aim :</t>
   </si>
   <si>
-    <t>To examine the firm's financial projections along with its competitors to determine if it is a SMART investment or not</t>
-  </si>
-  <si>
     <t>Days in the period</t>
   </si>
   <si>
@@ -4510,6 +4507,9 @@
   </si>
   <si>
     <t>Reported ETR</t>
+  </si>
+  <si>
+    <t>To examine the firm's financial projections along with its competitors to determine if it is a SMART investment or not (For modelling purposes only )</t>
   </si>
 </sst>
 </file>
@@ -6873,13 +6873,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>110490</xdr:colOff>
+      <xdr:colOff>110491</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>20956</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>739141</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>45721</xdr:rowOff>
     </xdr:to>
@@ -7537,7 +7537,7 @@
       <c r="D6" s="207"/>
       <c r="E6" s="28"/>
       <c r="F6" s="206" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="G6" s="206"/>
       <c r="H6" s="206"/>
@@ -8232,7 +8232,7 @@
         <v>644</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>645</v>
+        <v>1382</v>
       </c>
       <c r="C30" s="21"/>
       <c r="D30" s="21"/>
@@ -9444,16 +9444,16 @@
         <v>46197</v>
       </c>
       <c r="B14" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C14" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D14" t="s">
         <v>1208</v>
       </c>
-      <c r="D14" t="s">
-        <v>1209</v>
-      </c>
       <c r="E14" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
   </sheetData>
@@ -9478,7 +9478,7 @@
     </row>
     <row r="2" spans="3:23" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="W2" s="16"/>
     </row>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="7" spans="3:23" x14ac:dyDescent="0.3">
       <c r="U7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8" spans="3:23" x14ac:dyDescent="0.3">
       <c r="U8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9" spans="3:23" x14ac:dyDescent="0.3">
       <c r="U9" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="10" spans="3:23" x14ac:dyDescent="0.3">
       <c r="U10" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W10">
         <v>3284.1</v>
@@ -9537,7 +9537,7 @@
     </row>
     <row r="13" spans="3:23" x14ac:dyDescent="0.3">
       <c r="U13" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="W13">
         <v>2231.6999999999998</v>
@@ -9553,7 +9553,7 @@
     </row>
     <row r="15" spans="3:23" x14ac:dyDescent="0.3">
       <c r="U15" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="W15" s="46">
         <f>W12-W13-W14</f>
@@ -9570,7 +9570,7 @@
     </row>
     <row r="17" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U17" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="W17">
         <v>246.8</v>
@@ -9578,7 +9578,7 @@
     </row>
     <row r="18" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U18" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="W18">
         <v>-1.3</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="19" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U19" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="W19" s="46">
         <f>W15-W16-W17+W18</f>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="21" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U21" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="23" spans="21:23" x14ac:dyDescent="0.3">
@@ -9611,12 +9611,12 @@
     </row>
     <row r="24" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U24" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="25" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U25" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="W25">
         <v>0.6</v>
@@ -9624,7 +9624,7 @@
     </row>
     <row r="26" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U26" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W26">
         <v>-102.7</v>
@@ -9632,7 +9632,7 @@
     </row>
     <row r="27" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U27" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="W27" s="46">
         <f>SUM(W23:W26)</f>
@@ -9641,7 +9641,7 @@
     </row>
     <row r="28" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U28" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="W28">
         <v>-55.7</v>
@@ -9649,7 +9649,7 @@
     </row>
     <row r="29" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U29" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="W29" s="47">
         <f>SUM(W27:W28)</f>
@@ -9658,13 +9658,13 @@
     </row>
     <row r="30" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U30" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="W30" s="2"/>
     </row>
     <row r="31" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U31" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="W31" s="2"/>
     </row>
@@ -9676,12 +9676,12 @@
     </row>
     <row r="34" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U34" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="35" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U35" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="W35" s="47">
         <f>SUM(W33:W34)</f>
@@ -9690,7 +9690,7 @@
     </row>
     <row r="36" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U36" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="37" spans="21:23" x14ac:dyDescent="0.3">
@@ -9711,42 +9711,42 @@
     </row>
     <row r="39" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U39" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="40" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U40" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="41" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U41" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="44" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U44" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="45" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U45" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="46" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U46" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="47" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U47" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="48" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U48" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="W48">
         <v>444.5</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="49" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U49" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="W49">
         <v>-1</v>
@@ -9762,7 +9762,7 @@
     </row>
     <row r="50" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U50" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="W50">
         <v>136.80000000000001</v>
@@ -9770,7 +9770,7 @@
     </row>
     <row r="51" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U51" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="W51">
         <v>196.6</v>
@@ -9778,7 +9778,7 @@
     </row>
     <row r="52" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U52" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="W52">
         <v>0.4</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="55" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U55" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W55">
         <v>1.1000000000000001</v>
@@ -9804,7 +9804,7 @@
     </row>
     <row r="56" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U56" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="W56">
         <v>-9.6</v>
@@ -9812,7 +9812,7 @@
     </row>
     <row r="57" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U57" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="W57">
         <v>205.4</v>
@@ -9820,7 +9820,7 @@
     </row>
     <row r="58" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U58" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W58">
         <v>-29.5</v>
@@ -9828,7 +9828,7 @@
     </row>
     <row r="59" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U59" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="W59">
         <v>-22.9</v>
@@ -9846,7 +9846,7 @@
     </row>
     <row r="61" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U61" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="W61">
         <v>-113.2</v>
@@ -9854,7 +9854,7 @@
     </row>
     <row r="62" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U62" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="W62" s="47">
         <f>SUM(W60:W61)</f>
@@ -9863,12 +9863,12 @@
     </row>
     <row r="63" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U63" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="64" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U64" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="W64">
         <v>-146.30000000000001</v>
@@ -9876,7 +9876,7 @@
     </row>
     <row r="65" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U65" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="W65">
         <v>1.7</v>
@@ -9884,7 +9884,7 @@
     </row>
     <row r="66" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U66" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="W66" s="46">
         <f>SUM(W64:W65)</f>
@@ -9902,7 +9902,7 @@
     </row>
     <row r="68" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U68" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="W68">
         <v>28.4</v>
@@ -9919,17 +9919,17 @@
     </row>
     <row r="70" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U70" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="71" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U71" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="72" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U72" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="W72">
         <v>3.9</v>
@@ -9937,12 +9937,12 @@
     </row>
     <row r="73" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U73" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="74" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U74" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="W74">
         <v>-2.4</v>
@@ -9950,12 +9950,12 @@
     </row>
     <row r="75" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U75" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="78" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U78" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W78" s="47">
         <f>SUM(W66:W76)</f>
@@ -9964,12 +9964,12 @@
     </row>
     <row r="79" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U79" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="80" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U80" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W80">
         <v>-19.3</v>
@@ -9977,7 +9977,7 @@
     </row>
     <row r="81" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U81" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="W81">
         <v>-189</v>
@@ -9994,7 +9994,7 @@
     </row>
     <row r="83" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U83" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="84" spans="21:23" x14ac:dyDescent="0.3">
@@ -10005,7 +10005,7 @@
     </row>
     <row r="85" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U85" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="W85">
         <v>-40</v>
@@ -10013,17 +10013,17 @@
     </row>
     <row r="86" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U86" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="87" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U87" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="88" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U88" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="W88">
         <v>-171</v>
@@ -10031,7 +10031,7 @@
     </row>
     <row r="89" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U89" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="W89">
         <v>-101.6</v>
@@ -10039,7 +10039,7 @@
     </row>
     <row r="90" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U90" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="W90">
         <v>0.5</v>
@@ -10047,17 +10047,17 @@
     </row>
     <row r="92" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U92" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="93" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U93" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="94" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U94" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="W94">
         <v>126</v>
@@ -10065,12 +10065,12 @@
     </row>
     <row r="95" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U95" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="96" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U96" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="97" spans="21:23" x14ac:dyDescent="0.3">
@@ -10087,7 +10087,7 @@
     </row>
     <row r="99" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U99" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W99">
         <v>52.9</v>
@@ -10095,12 +10095,12 @@
     </row>
     <row r="100" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U100" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="101" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U101" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W101">
         <v>-0.3</v>
@@ -10122,32 +10122,32 @@
     </row>
     <row r="104" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U104" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="105" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U105" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="106" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U106" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="107" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U107" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="108" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U108" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="109" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U109" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="110" spans="21:23" x14ac:dyDescent="0.3">
@@ -10162,7 +10162,7 @@
     </row>
     <row r="112" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U112" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W112">
         <v>720.1</v>
@@ -10170,7 +10170,7 @@
     </row>
     <row r="113" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U113" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="W113">
         <v>5</v>
@@ -10178,7 +10178,7 @@
     </row>
     <row r="114" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U114" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W114">
         <v>99.2</v>
@@ -10186,7 +10186,7 @@
     </row>
     <row r="115" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U115" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="W115">
         <v>39.4</v>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="116" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U116" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="W116">
         <v>70.400000000000006</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="117" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U117" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="W117" s="47">
         <f>SUM(W110:W116)</f>
@@ -10211,12 +10211,12 @@
     </row>
     <row r="118" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U118" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="119" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U119" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="121" spans="21:23" x14ac:dyDescent="0.3">
@@ -10226,7 +10226,7 @@
     </row>
     <row r="122" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U122" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W122">
         <v>1108.0999999999999</v>
@@ -10234,7 +10234,7 @@
     </row>
     <row r="123" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U123" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="W123">
         <v>24.3</v>
@@ -10242,7 +10242,7 @@
     </row>
     <row r="124" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U124" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W124">
         <v>11.1</v>
@@ -10250,7 +10250,7 @@
     </row>
     <row r="125" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U125" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="W125">
         <v>608.20000000000005</v>
@@ -10258,12 +10258,12 @@
     </row>
     <row r="126" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U126" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="127" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U127" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="W127" s="47">
         <f>SUM(W121:W126)</f>
@@ -10272,12 +10272,12 @@
     </row>
     <row r="128" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U128" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="129" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U129" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="W129" s="2">
         <f>W127+W117</f>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="132" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U132" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W132">
         <v>93.4</v>
@@ -10294,7 +10294,7 @@
     </row>
     <row r="133" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U133" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="W133">
         <v>326</v>
@@ -10302,7 +10302,7 @@
     </row>
     <row r="134" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U134" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W134">
         <v>555.29999999999995</v>
@@ -10310,7 +10310,7 @@
     </row>
     <row r="135" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U135" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="W135">
         <v>170.1</v>
@@ -10318,7 +10318,7 @@
     </row>
     <row r="136" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U136" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="W136">
         <v>37.200000000000003</v>
@@ -10326,7 +10326,7 @@
     </row>
     <row r="137" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U137" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="W137">
         <v>14.8</v>
@@ -10334,7 +10334,7 @@
     </row>
     <row r="138" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U138" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="W138" s="47">
         <f>SUM(W132:W137)</f>
@@ -10346,12 +10346,12 @@
     </row>
     <row r="140" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U140" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="141" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U141" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="143" spans="21:23" x14ac:dyDescent="0.3">
@@ -10361,7 +10361,7 @@
     </row>
     <row r="144" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U144" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W144">
         <v>18.600000000000001</v>
@@ -10369,7 +10369,7 @@
     </row>
     <row r="145" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U145" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="W145">
         <v>1015.8</v>
@@ -10377,12 +10377,12 @@
     </row>
     <row r="146" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U146" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="147" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U147" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="W147">
         <v>28.9</v>
@@ -10390,12 +10390,12 @@
     </row>
     <row r="148" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U148" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="149" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U149" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="W149" s="47">
         <f>SUM(W142:W148)</f>
@@ -10404,13 +10404,13 @@
     </row>
     <row r="150" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U150" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="W150" s="2"/>
     </row>
     <row r="151" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U151" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="W151" s="2">
         <f>W129-W138-W149</f>
@@ -10419,33 +10419,33 @@
     </row>
     <row r="152" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U152" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="153" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U153" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="155" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U155" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="158" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U158" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="W158" s="2"/>
     </row>
     <row r="159" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U159" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="160" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U160" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="W160" s="33">
         <v>660.9</v>
@@ -10453,12 +10453,12 @@
     </row>
     <row r="161" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U161" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="162" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U162" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="W162">
         <f>W160-W151</f>
@@ -10467,17 +10467,17 @@
     </row>
     <row r="163" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U163" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="164" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U164" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="165" spans="21:23" x14ac:dyDescent="0.3">
       <c r="U165" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="173" spans="21:23" x14ac:dyDescent="0.3">
@@ -12597,7 +12597,7 @@
     </row>
     <row r="766" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C766" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E766" s="2"/>
       <c r="F766" s="2"/>
@@ -13038,7 +13038,7 @@
     </row>
     <row r="785" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C785" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E785" s="46">
         <f>SUM(E764:E784)</f>
@@ -13231,7 +13231,7 @@
     </row>
     <row r="792" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C792" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E792" s="2"/>
       <c r="F792" s="2"/>
@@ -13281,7 +13281,7 @@
     </row>
     <row r="795" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C795" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E795" s="46">
         <f>E791+E793+E794</f>
@@ -14095,7 +14095,7 @@
     </row>
     <row r="851" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C851" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E851" s="10">
         <f>E757/E753</f>
@@ -14124,7 +14124,7 @@
     </row>
     <row r="852" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C852" s="12" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E852" s="10">
         <f>E758/E753</f>
@@ -14375,7 +14375,7 @@
     </row>
     <row r="867" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C867" s="12" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E867" s="71"/>
       <c r="F867" s="71"/>
@@ -17498,7 +17498,7 @@
     </row>
     <row r="1060" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C1060" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E1060">
         <v>11.3</v>
@@ -17925,7 +17925,7 @@
     </row>
     <row r="1074" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C1074" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E1074" s="2">
         <f>E1156+E1148</f>
@@ -18745,7 +18745,7 @@
     </row>
     <row r="1130" spans="3:26" ht="21" x14ac:dyDescent="0.4">
       <c r="C1130" s="54" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E1130" s="2">
         <f>E1127-E1111+E1098+E1094</f>
@@ -18798,7 +18798,7 @@
     </row>
     <row r="1133" spans="3:26" ht="23.4" x14ac:dyDescent="0.45">
       <c r="C1133" s="63" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K1133">
         <v>2022</v>
@@ -18824,7 +18824,7 @@
         <v>594</v>
       </c>
       <c r="D1134" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E1134">
         <v>1432.4</v>
@@ -18923,7 +18923,7 @@
         <v>583</v>
       </c>
       <c r="D1137" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E1137">
         <f>1526.7+865</f>
@@ -19063,7 +19063,7 @@
         <v>586</v>
       </c>
       <c r="D1141" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E1141">
         <v>673</v>
@@ -19196,7 +19196,7 @@
         <v>588</v>
       </c>
       <c r="D1145" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E1145">
         <v>249.4</v>
@@ -19291,7 +19291,7 @@
         <v>241</v>
       </c>
       <c r="D1148" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E1148">
         <v>39.1</v>
@@ -19383,7 +19383,7 @@
         <v>242</v>
       </c>
       <c r="D1151" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E1151">
         <v>76.2</v>
@@ -19570,10 +19570,10 @@
     </row>
     <row r="1156" spans="3:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1156" s="67" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D1156" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F1156">
         <v>239</v>
@@ -19682,7 +19682,7 @@
     </row>
     <row r="1161" spans="3:26" ht="21" x14ac:dyDescent="0.4">
       <c r="C1161" s="54" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E1161" s="2"/>
       <c r="F1161" s="2"/>
@@ -20119,7 +20119,7 @@
     </row>
     <row r="1202" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1202" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="I1202">
         <v>859</v>
@@ -20127,7 +20127,7 @@
     </row>
     <row r="1203" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1203" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="I1203" s="2">
         <f>I1200+I1202</f>
@@ -20136,7 +20136,7 @@
     </row>
     <row r="1204" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1204" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="I1204">
         <v>439</v>
@@ -20765,7 +20765,7 @@
     </row>
     <row r="1263" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C1263" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="I1263">
         <v>125</v>
@@ -20773,7 +20773,7 @@
     </row>
     <row r="1264" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C1264" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="I1264">
         <v>130</v>
@@ -20787,7 +20787,7 @@
     </row>
     <row r="1266" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1266" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="I1266">
         <v>170</v>
@@ -20795,7 +20795,7 @@
     </row>
     <row r="1267" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1267" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I1267">
         <v>125</v>
@@ -20809,7 +20809,7 @@
     </row>
     <row r="1270" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1270" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I1270">
         <f>I1263+I1266</f>
@@ -20818,7 +20818,7 @@
     </row>
     <row r="1271" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1271" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="I1271">
         <f>I1264+I1267</f>
@@ -20836,12 +20836,12 @@
     </row>
     <row r="1275" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1275" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="1276" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1276" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="I1276" s="10">
         <v>3.1E-2</v>
@@ -20849,7 +20849,7 @@
     </row>
     <row r="1277" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1277" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I1277" s="10">
         <v>1.7999999999999999E-2</v>
@@ -20857,7 +20857,7 @@
     </row>
     <row r="1278" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1278" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="I1278" s="10">
         <v>8.0000000000000002E-3</v>
@@ -20873,7 +20873,7 @@
     </row>
     <row r="1280" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1280" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="I1280" s="10">
         <v>0.16500000000000001</v>
@@ -20881,7 +20881,7 @@
     </row>
     <row r="1283" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1283" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="1284" spans="3:9" x14ac:dyDescent="0.3">
@@ -20897,7 +20897,7 @@
     </row>
     <row r="1285" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1285" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1285">
         <v>48</v>
@@ -20908,7 +20908,7 @@
     </row>
     <row r="1286" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1286" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1286">
         <v>13</v>
@@ -20919,7 +20919,7 @@
     </row>
     <row r="1287" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1287" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1287">
         <v>61</v>
@@ -20943,7 +20943,7 @@
     </row>
     <row r="1293" spans="3:9" ht="21" x14ac:dyDescent="0.4">
       <c r="C1293" s="54" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="1294" spans="3:9" x14ac:dyDescent="0.3">
@@ -20965,17 +20965,17 @@
     </row>
     <row r="1297" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1297" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1298" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1298" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="1299" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1299" s="39" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="1300" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -20985,7 +20985,7 @@
     </row>
     <row r="1301" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1301" s="67" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E1301">
         <v>4862</v>
@@ -21005,7 +21005,7 @@
     </row>
     <row r="1302" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1302" s="67" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F1302">
         <v>370</v>
@@ -21016,7 +21016,7 @@
     </row>
     <row r="1303" spans="3:9" ht="18" x14ac:dyDescent="0.35">
       <c r="C1303" s="66" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F1303">
         <v>5146</v>
@@ -21039,7 +21039,7 @@
     </row>
     <row r="1306" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1306" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="1307" spans="3:9" x14ac:dyDescent="0.3">
@@ -21064,12 +21064,12 @@
     </row>
     <row r="1309" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1309" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="1310" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1310" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1312" spans="3:9" x14ac:dyDescent="0.3">
@@ -21094,7 +21094,7 @@
     </row>
     <row r="1314" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1314" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F1314">
         <v>-36</v>
@@ -21111,7 +21111,7 @@
     </row>
     <row r="1316" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1316" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F1316">
         <v>204</v>
@@ -21128,7 +21128,7 @@
     </row>
     <row r="1317" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1317" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1317" s="11">
         <v>0.11</v>
@@ -21139,7 +21139,7 @@
     </row>
     <row r="1318" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1318" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E1318">
         <v>65</v>
@@ -21152,7 +21152,7 @@
     </row>
     <row r="1321" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1321" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G1321">
         <v>2429</v>
@@ -21185,7 +21185,7 @@
     </row>
     <row r="1326" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1326" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G1326">
         <v>731</v>
@@ -21199,7 +21199,7 @@
     </row>
     <row r="1327" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1327" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G1327">
         <v>95</v>
@@ -21227,7 +21227,7 @@
     </row>
     <row r="1330" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1330" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E1330">
         <v>588</v>
@@ -21238,7 +21238,7 @@
     </row>
     <row r="1333" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1333" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="1334" spans="3:9" x14ac:dyDescent="0.3">
@@ -21263,7 +21263,7 @@
     </row>
     <row r="1335" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1335" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E1335">
         <v>3.5</v>
@@ -21283,7 +21283,7 @@
     </row>
     <row r="1336" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1336" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E1336">
         <v>1.9</v>
@@ -21303,7 +21303,7 @@
     </row>
     <row r="1337" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1337" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E1337" s="2">
         <f>SUM(E1334:E1336)</f>
@@ -21343,7 +21343,7 @@
     </row>
     <row r="1341" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1341" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F1341">
         <v>26.5</v>
@@ -21360,7 +21360,7 @@
     </row>
     <row r="1342" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1342" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F1342">
         <v>21.1</v>
@@ -21377,7 +21377,7 @@
     </row>
     <row r="1343" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1343" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E1343" s="47">
         <f>E1341-E1342</f>
@@ -21409,7 +21409,7 @@
     </row>
     <row r="1345" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1345" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E1345" s="2"/>
       <c r="F1345" s="2"/>
@@ -21419,7 +21419,7 @@
     </row>
     <row r="1346" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1346" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E1346" s="2"/>
       <c r="F1346" s="2">
@@ -21437,7 +21437,7 @@
     </row>
     <row r="1347" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1347" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E1347" s="2"/>
       <c r="F1347">
@@ -21455,7 +21455,7 @@
     </row>
     <row r="1348" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1348" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E1348" s="2"/>
       <c r="F1348">
@@ -21473,7 +21473,7 @@
     </row>
     <row r="1349" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1349" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E1349" s="2"/>
       <c r="F1349">
@@ -21491,7 +21491,7 @@
     </row>
     <row r="1350" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1350" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E1350" s="47">
         <f>SUM(E1347:E1349)</f>
@@ -21530,7 +21530,7 @@
     </row>
     <row r="1356" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1356" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J1356" s="10">
         <v>2.1999999999999999E-2</v>
@@ -21564,7 +21564,7 @@
     </row>
     <row r="1360" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1360" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E1360">
         <v>-50</v>
@@ -21584,7 +21584,7 @@
     </row>
     <row r="1361" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1361" s="67" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E1361" s="46">
         <f>SUM(E1359:E1360)</f>
@@ -21609,7 +21609,7 @@
     </row>
     <row r="1362" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1362" s="67" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E1362">
         <v>-32</v>
@@ -21662,7 +21662,7 @@
     </row>
     <row r="1365" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1365" s="67" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E1365">
         <f>-(E1360+E1362)</f>
@@ -21687,7 +21687,7 @@
     </row>
     <row r="1366" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1366" s="67" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E1366">
         <v>32</v>
@@ -21695,7 +21695,7 @@
     </row>
     <row r="1367" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1367" s="67" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E1367">
         <v>50</v>
@@ -21706,7 +21706,7 @@
     </row>
     <row r="1369" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1369" s="67" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F1369">
         <v>870</v>
@@ -21717,12 +21717,12 @@
     </row>
     <row r="1370" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1370" s="39" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="1371" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1371" s="67" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1371">
         <v>10</v>
@@ -21733,7 +21733,7 @@
     </row>
     <row r="1372" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1372" s="67" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I1372">
         <v>-8</v>
@@ -21741,7 +21741,7 @@
     </row>
     <row r="1373" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1373" s="67" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1373">
         <v>-13</v>
@@ -21752,7 +21752,7 @@
     </row>
     <row r="1374" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1374" s="67" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1374">
         <v>2</v>
@@ -21794,7 +21794,7 @@
     </row>
     <row r="1377" spans="3:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="C1377" s="87" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E1377">
         <v>4862</v>
@@ -21834,7 +21834,7 @@
     </row>
     <row r="1379" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1379" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E1379">
         <v>-50</v>
@@ -21854,7 +21854,7 @@
     </row>
     <row r="1380" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1380" s="67" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E1380" s="46">
         <f>SUM(E1378:E1379)</f>
@@ -21879,7 +21879,7 @@
     </row>
     <row r="1381" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1381" s="67" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E1381">
         <v>-32</v>
@@ -21924,7 +21924,7 @@
     </row>
     <row r="1383" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1383" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E1383" s="2">
         <v>-146</v>
@@ -21944,7 +21944,7 @@
     </row>
     <row r="1384" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1384" s="67" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E1384" s="47">
         <f>E1382+E1383</f>
@@ -21969,7 +21969,7 @@
     </row>
     <row r="1385" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1385" s="67" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E1385" s="2" t="s">
         <v>178</v>
@@ -21978,13 +21978,13 @@
         <v>576.79999999999995</v>
       </c>
       <c r="G1385" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1385" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="I1385" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="I1385" s="2" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="1386" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -21997,7 +21997,7 @@
     </row>
     <row r="1387" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1387" s="67" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E1387" s="2"/>
       <c r="F1387" s="2"/>
@@ -22007,7 +22007,7 @@
     </row>
     <row r="1388" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1388" s="67" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E1388" s="2"/>
       <c r="F1388" s="2"/>
@@ -22035,29 +22035,29 @@
     </row>
     <row r="1391" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1391" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G1391" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1391" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I1391" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="1392" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1392" t="s">
+        <v>726</v>
+      </c>
+      <c r="I1392" t="s">
         <v>727</v>
-      </c>
-      <c r="I1392" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="1393" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1393" s="67" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E1393" s="2"/>
       <c r="F1393" s="2">
@@ -22071,7 +22071,7 @@
     </row>
     <row r="1395" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1395" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E1395" s="10">
         <f>-E1383/E1382</f>
@@ -22099,7 +22099,7 @@
     </row>
     <row r="1400" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1400" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E1400" s="11">
         <v>0.22</v>
@@ -22141,7 +22141,7 @@
     </row>
     <row r="1403" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1403" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E1403">
         <v>823</v>
@@ -22162,7 +22162,7 @@
     </row>
     <row r="1404" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1404" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E1404" s="11"/>
       <c r="F1404" s="11"/>
@@ -22175,7 +22175,7 @@
     </row>
     <row r="1405" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1405" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E1405">
         <v>111</v>
@@ -22195,7 +22195,7 @@
     </row>
     <row r="1406" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1406" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E1406">
         <v>-184</v>
@@ -22224,7 +22224,7 @@
     </row>
     <row r="1407" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1407" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E1407">
         <v>-183</v>
@@ -22244,12 +22244,12 @@
     </row>
     <row r="1408" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C1408" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="1409" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1409" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E1409">
         <v>-125</v>
@@ -22269,7 +22269,7 @@
     </row>
     <row r="1410" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1410" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F1410">
         <v>-91</v>
@@ -22286,7 +22286,7 @@
     </row>
     <row r="1411" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1411" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E1411">
         <v>-79</v>
@@ -22294,7 +22294,7 @@
     </row>
     <row r="1412" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1412" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E1412" s="47">
         <f>SUM(E1403:E1411)</f>
@@ -22319,7 +22319,7 @@
     </row>
     <row r="1413" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1413" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F1413">
         <v>-237</v>
@@ -22336,7 +22336,7 @@
     </row>
     <row r="1414" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1414" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E1414">
         <v>-353</v>
@@ -22356,7 +22356,7 @@
     </row>
     <row r="1415" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1415" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E1415" s="47">
         <f>-SUM(E1413:E1414)</f>
@@ -22381,7 +22381,7 @@
     </row>
     <row r="1417" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1417" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E1417">
         <f>E1412-E1415</f>
@@ -22412,7 +22412,7 @@
     </row>
     <row r="1420" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1420" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G1420">
         <v>198</v>
@@ -22426,7 +22426,7 @@
     </row>
     <row r="1421" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1421" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E1421">
         <v>1977</v>
@@ -22446,7 +22446,7 @@
     </row>
     <row r="1422" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1422" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F1422">
         <v>1255</v>
@@ -22457,7 +22457,7 @@
     </row>
     <row r="1423" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1423" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E1423">
         <v>-815</v>
@@ -22471,7 +22471,7 @@
     </row>
     <row r="1424" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1424" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E1424">
         <v>1281</v>
@@ -22488,7 +22488,7 @@
     </row>
     <row r="1427" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1427" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E1427">
         <v>1436</v>
@@ -22496,7 +22496,7 @@
     </row>
     <row r="1428" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1428" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E1428">
         <v>190</v>
@@ -22504,7 +22504,7 @@
     </row>
     <row r="1429" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1429" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E1429">
         <v>102</v>
@@ -22512,7 +22512,7 @@
     </row>
     <row r="1430" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1430" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E1430">
         <v>249</v>
@@ -22531,7 +22531,7 @@
     </row>
     <row r="1434" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1434" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E1434">
         <v>249</v>
@@ -22539,7 +22539,7 @@
     </row>
     <row r="1435" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1435" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E1435">
         <v>-27</v>
@@ -22547,7 +22547,7 @@
     </row>
     <row r="1436" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1436" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E1436">
         <v>-49</v>
@@ -22555,7 +22555,7 @@
     </row>
     <row r="1437" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1437" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E1437" s="48">
         <f>SUM(E1434:E1436)</f>
@@ -22564,7 +22564,7 @@
     </row>
     <row r="1438" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1438" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E1438">
         <v>-31</v>
@@ -22572,7 +22572,7 @@
     </row>
     <row r="1439" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C1439" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E1439" s="33">
         <f>SUM(E1437:E1438)</f>
@@ -22581,7 +22581,7 @@
     </row>
     <row r="1442" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1442" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="1444" spans="3:10" x14ac:dyDescent="0.3">
@@ -22594,7 +22594,7 @@
     </row>
     <row r="1445" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1445" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J1445">
         <v>500</v>
@@ -22602,7 +22602,7 @@
     </row>
     <row r="1446" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1446" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="I1446">
         <v>196</v>
@@ -22610,7 +22610,7 @@
     </row>
     <row r="1448" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1448" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J1448">
         <v>978</v>
@@ -22618,7 +22618,7 @@
     </row>
     <row r="1451" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1451" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E1451">
         <f>-E1407</f>
@@ -22643,7 +22643,7 @@
     </row>
     <row r="1452" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1452" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F1452">
         <v>-92</v>
@@ -22654,7 +22654,7 @@
     </row>
     <row r="1453" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1453" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F1453">
         <v>-89</v>
@@ -22665,7 +22665,7 @@
     </row>
     <row r="1454" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1454" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F1454">
         <v>-44</v>
@@ -22676,12 +22676,12 @@
     </row>
     <row r="1457" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1457" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="1458" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1458" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="I1458">
         <v>114</v>
@@ -22695,7 +22695,7 @@
     </row>
     <row r="1459" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1459" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J1459">
         <v>790</v>
@@ -22703,7 +22703,7 @@
     </row>
     <row r="1460" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1460" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="J1460">
         <v>1125</v>
@@ -22711,7 +22711,7 @@
     </row>
     <row r="1462" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1462" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E1462" s="2">
         <f>E1471</f>
@@ -22728,7 +22728,7 @@
     </row>
     <row r="1463" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1463" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G1463">
         <v>84</v>
@@ -22736,7 +22736,7 @@
     </row>
     <row r="1464" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1464" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="G1464">
         <v>716</v>
@@ -22747,7 +22747,7 @@
     </row>
     <row r="1467" spans="3:14" ht="23.4" x14ac:dyDescent="0.45">
       <c r="C1467" s="91" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E1467">
         <v>90</v>
@@ -22758,7 +22758,7 @@
     </row>
     <row r="1469" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1469" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E1469">
         <v>636</v>
@@ -22778,7 +22778,7 @@
     </row>
     <row r="1470" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1470" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E1470">
         <v>90</v>
@@ -22798,7 +22798,7 @@
     </row>
     <row r="1471" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1471" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E1471">
         <v>658</v>
@@ -22818,7 +22818,7 @@
     </row>
     <row r="1472" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C1472" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F1472">
         <v>1255</v>
@@ -22835,7 +22835,7 @@
     </row>
     <row r="1473" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C1473" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E1473">
         <v>1281</v>
@@ -22855,7 +22855,7 @@
     </row>
     <row r="1474" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C1474" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E1474">
         <v>-815</v>
@@ -22875,7 +22875,7 @@
     </row>
     <row r="1475" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C1475" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E1475">
         <v>157</v>
@@ -22903,7 +22903,7 @@
     </row>
     <row r="1477" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C1477" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E1477">
         <v>-600</v>
@@ -22923,7 +22923,7 @@
     </row>
     <row r="1478" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C1478" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E1478">
         <v>639</v>
@@ -22943,7 +22943,7 @@
     </row>
     <row r="1479" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C1479" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E1479">
         <v>-1057</v>
@@ -24317,7 +24317,7 @@
     </row>
     <row r="1635" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1635" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E1635">
         <v>-50</v>
@@ -24337,7 +24337,7 @@
     </row>
     <row r="1636" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1636" s="67" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E1636" s="46">
         <f>SUM(E1634:E1635)</f>
@@ -24362,7 +24362,7 @@
     </row>
     <row r="1637" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1637" s="67" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E1637">
         <v>-32</v>
@@ -24415,7 +24415,7 @@
     </row>
     <row r="1640" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1640" s="67" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E1640">
         <f>-(E1635+E1637)</f>
@@ -24440,7 +24440,7 @@
     </row>
     <row r="1641" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1641" s="67" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E1641">
         <v>32</v>
@@ -24448,7 +24448,7 @@
     </row>
     <row r="1642" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1642" s="67" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E1642">
         <v>50</v>
@@ -24459,7 +24459,7 @@
     </row>
     <row r="1644" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1644" s="67" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F1644">
         <v>870</v>
@@ -24470,12 +24470,12 @@
     </row>
     <row r="1645" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1645" s="39" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="1646" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1646" s="67" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1646">
         <v>10</v>
@@ -24486,7 +24486,7 @@
     </row>
     <row r="1647" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1647" s="67" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I1647">
         <v>-8</v>
@@ -24494,7 +24494,7 @@
     </row>
     <row r="1648" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1648" s="67" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1648">
         <v>-13</v>
@@ -24505,7 +24505,7 @@
     </row>
     <row r="1649" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1649" s="67" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1649">
         <v>2</v>
@@ -24547,7 +24547,7 @@
     </row>
     <row r="1652" spans="3:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="C1652" s="87" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E1652">
         <v>4862</v>
@@ -24587,7 +24587,7 @@
     </row>
     <row r="1654" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1654" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E1654">
         <v>-50</v>
@@ -24607,7 +24607,7 @@
     </row>
     <row r="1655" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1655" s="67" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E1655" s="46">
         <f>SUM(E1653:E1654)</f>
@@ -24632,7 +24632,7 @@
     </row>
     <row r="1656" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1656" s="67" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E1656">
         <v>-32</v>
@@ -24677,7 +24677,7 @@
     </row>
     <row r="1658" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1658" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E1658" s="2">
         <v>-146</v>
@@ -24697,7 +24697,7 @@
     </row>
     <row r="1659" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1659" s="67" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E1659" s="47">
         <f>E1657+E1658</f>
@@ -24722,7 +24722,7 @@
     </row>
     <row r="1660" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1660" s="67" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E1660" s="2" t="s">
         <v>178</v>
@@ -24731,13 +24731,13 @@
         <v>576.79999999999995</v>
       </c>
       <c r="G1660" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1660" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="I1660" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="I1660" s="2" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="1661" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -24750,7 +24750,7 @@
     </row>
     <row r="1662" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1662" s="67" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E1662" s="2"/>
       <c r="F1662" s="2"/>
@@ -24760,7 +24760,7 @@
     </row>
     <row r="1663" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1663" s="67" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E1663" s="2"/>
       <c r="F1663" s="2"/>
@@ -24788,29 +24788,29 @@
     </row>
     <row r="1666" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1666" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G1666" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1666" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I1666" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="1667" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1667" t="s">
+        <v>726</v>
+      </c>
+      <c r="I1667" t="s">
         <v>727</v>
-      </c>
-      <c r="I1667" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="1668" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C1668" s="67" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E1668" s="2"/>
       <c r="F1668" s="2">
@@ -24824,7 +24824,7 @@
     </row>
     <row r="1670" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1670" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E1670" s="10">
         <f>-E1658/E1657</f>
@@ -24852,7 +24852,7 @@
     </row>
     <row r="1675" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1675" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E1675" s="11">
         <v>0.22</v>
@@ -24891,7 +24891,7 @@
     </row>
     <row r="1678" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1678" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E1678">
         <v>823</v>
@@ -24912,7 +24912,7 @@
     </row>
     <row r="1679" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1679" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E1679" s="11"/>
       <c r="F1679" s="11"/>
@@ -24925,7 +24925,7 @@
     </row>
     <row r="1680" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C1680" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E1680">
         <v>111</v>
@@ -24945,7 +24945,7 @@
     </row>
     <row r="1681" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1681" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E1681">
         <v>-184</v>
@@ -24974,7 +24974,7 @@
     </row>
     <row r="1682" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1682" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E1682">
         <v>-183</v>
@@ -24994,12 +24994,12 @@
     </row>
     <row r="1683" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1683" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="1684" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1684" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E1684">
         <v>-125</v>
@@ -25019,7 +25019,7 @@
     </row>
     <row r="1685" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1685" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F1685">
         <v>-91</v>
@@ -25036,7 +25036,7 @@
     </row>
     <row r="1686" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1686" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E1686">
         <v>-79</v>
@@ -25044,7 +25044,7 @@
     </row>
     <row r="1687" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1687" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E1687" s="47">
         <f>SUM(E1678:E1686)</f>
@@ -25069,7 +25069,7 @@
     </row>
     <row r="1688" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1688" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F1688">
         <v>-237</v>
@@ -25086,7 +25086,7 @@
     </row>
     <row r="1689" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1689" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E1689">
         <v>-353</v>
@@ -25106,7 +25106,7 @@
     </row>
     <row r="1690" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1690" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E1690" s="47">
         <f>-SUM(E1688:E1689)</f>
@@ -25131,7 +25131,7 @@
     </row>
     <row r="1692" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C1692" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E1692">
         <f>E1687-E1690</f>
@@ -26150,7 +26150,7 @@
     </row>
     <row r="1788" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1788" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F1788">
         <v>0.4</v>
@@ -26167,7 +26167,7 @@
     </row>
     <row r="1789" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C1789" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E1789">
         <v>4.3</v>
@@ -27483,7 +27483,7 @@
     </row>
     <row r="1892" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1892" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="1893" spans="1:9" x14ac:dyDescent="0.3">
@@ -27731,7 +27731,7 @@
     </row>
     <row r="1916" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B1916" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="1917" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
@@ -28420,7 +28420,7 @@
     </row>
     <row r="1964" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1964" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="1966" spans="1:9" x14ac:dyDescent="0.3">
@@ -28733,7 +28733,7 @@
     </row>
     <row r="1993" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B1993" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="1994" spans="2:10" ht="25.8" x14ac:dyDescent="0.5">
@@ -29680,7 +29680,7 @@
     </row>
     <row r="2046" spans="3:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="C2046" s="63" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="2048" spans="3:9" x14ac:dyDescent="0.3">
@@ -29894,7 +29894,7 @@
     </row>
     <row r="2063" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2063" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E2063">
         <v>-50</v>
@@ -29914,7 +29914,7 @@
     </row>
     <row r="2064" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C2064" s="67" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E2064" s="46">
         <f>SUM(E2062:E2063)</f>
@@ -29939,7 +29939,7 @@
     </row>
     <row r="2065" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C2065" s="67" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E2065">
         <v>-32</v>
@@ -29992,7 +29992,7 @@
     </row>
     <row r="2068" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C2068" s="67" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E2068">
         <f>-(E2063+E2065)</f>
@@ -30017,7 +30017,7 @@
     </row>
     <row r="2069" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C2069" s="67" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E2069">
         <v>32</v>
@@ -30037,7 +30037,7 @@
     </row>
     <row r="2070" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C2070" s="67" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E2070">
         <v>50</v>
@@ -30145,7 +30145,7 @@
     </row>
     <row r="2079" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2079" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="2082" spans="3:9" ht="25.8" x14ac:dyDescent="0.5">
@@ -30462,7 +30462,7 @@
     </row>
     <row r="2113" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2113" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E2113">
         <f>E2109</f>
@@ -30487,7 +30487,7 @@
     </row>
     <row r="2114" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2114" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E2114">
         <f>AVERAGE(D2084:E2084)</f>
@@ -30512,7 +30512,7 @@
     </row>
     <row r="2115" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2115" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F2115">
         <f>F2113/F2114</f>
@@ -30533,7 +30533,7 @@
     </row>
     <row r="2116" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2116" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I2116">
         <f>AVERAGE(E2115:I2115)</f>
@@ -30542,7 +30542,7 @@
     </row>
     <row r="2122" spans="3:9" ht="31.2" x14ac:dyDescent="0.6">
       <c r="C2122" s="64" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="2123" spans="3:9" x14ac:dyDescent="0.3">
@@ -31605,12 +31605,12 @@
     </row>
     <row r="2214" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2214" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="2215" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2215" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E2215">
         <f>E2142</f>
@@ -31635,7 +31635,7 @@
     </row>
     <row r="2216" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2216" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E2216">
         <f>E2185</f>
@@ -31683,7 +31683,7 @@
     </row>
     <row r="2219" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2219" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E2219">
         <f>E2143</f>
@@ -31708,7 +31708,7 @@
     </row>
     <row r="2221" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2221" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E2221">
         <f>E751</f>
@@ -31738,17 +31738,17 @@
     </row>
     <row r="2223" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2223" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="2224" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2224" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="2225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2225" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E2225">
         <v>39.1</v>
@@ -31768,7 +31768,7 @@
     </row>
     <row r="2226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2226" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F2226">
         <v>35.6</v>
@@ -31785,7 +31785,7 @@
     </row>
     <row r="2228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2228" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F2228">
         <v>110.3</v>
@@ -31796,33 +31796,33 @@
     </row>
     <row r="2229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2229" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C2229" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="2230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2230" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C2230" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="2231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2231" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="2232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2232" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="2233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2233" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D2233" s="2"/>
       <c r="E2233" s="2"/>
@@ -31833,42 +31833,42 @@
     </row>
     <row r="2234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2234" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="2235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2235" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2236" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="2237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2237" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="2238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2238" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="2239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2239" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="2241" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2241" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="2242" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C2242" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D2242" s="2"/>
       <c r="E2242" s="2"/>
@@ -31879,22 +31879,22 @@
     </row>
     <row r="2243" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C2243" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="2244" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C2244" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="2246" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C2246" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="2249" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C2249" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D2249" s="2"/>
       <c r="E2249" s="2"/>
@@ -31987,7 +31987,7 @@
     </row>
     <row r="2254" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C2254" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D2254" s="2"/>
       <c r="E2254" s="2"/>
@@ -32102,7 +32102,7 @@
     </row>
     <row r="2261" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C2261" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D2261" s="2"/>
       <c r="E2261" s="2"/>
@@ -33128,7 +33128,7 @@
     </row>
     <row r="2318" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2318" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E2318">
         <f>E2316-E2256</f>
@@ -33375,12 +33375,12 @@
     </row>
     <row r="2335" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2335" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="2336" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2336" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2336">
         <v>81.099999999999994</v>
@@ -33391,7 +33391,7 @@
     </row>
     <row r="2337" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2337" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2337">
         <v>0.3</v>
@@ -33402,7 +33402,7 @@
     </row>
     <row r="2340" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2340" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2340">
         <v>-21</v>
@@ -33416,7 +33416,7 @@
     </row>
     <row r="2342" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2342" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F2342">
         <f>G2342+G2267</f>
@@ -33455,7 +33455,7 @@
     </row>
     <row r="2346" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2346" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E2346">
         <f>F2256-E2256</f>
@@ -33480,7 +33480,7 @@
     </row>
     <row r="2348" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2348" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D2348">
         <f>AVERAGE(E2348:I2348)</f>
@@ -33558,7 +33558,7 @@
     </row>
     <row r="2350" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2350" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D2350" s="90">
         <f>AVERAGE(F2350:I2350)</f>
@@ -33596,12 +33596,12 @@
     </row>
     <row r="2353" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2353" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="2354" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2354" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D2354">
         <v>2.6147701652896566E-2</v>
@@ -33626,7 +33626,7 @@
     </row>
     <row r="2356" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2356" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I2356">
         <v>-29</v>
@@ -33634,7 +33634,7 @@
     </row>
     <row r="2360" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2360" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="2361" spans="3:10" x14ac:dyDescent="0.3">
@@ -33713,7 +33713,7 @@
     </row>
     <row r="2365" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2365" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2366" spans="3:10" x14ac:dyDescent="0.3">
@@ -33770,7 +33770,7 @@
     </row>
     <row r="2374" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2374" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="2375" spans="3:14" x14ac:dyDescent="0.3">
@@ -33815,7 +33815,7 @@
     </row>
     <row r="2383" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2383" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D2383" s="71">
         <f t="shared" ref="D2383:I2383" si="36">D2349/D749</f>
@@ -33864,7 +33864,7 @@
     </row>
     <row r="2384" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2384" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E2384" s="10">
         <f>E2383-D2383</f>
@@ -33947,7 +33947,7 @@
     </row>
     <row r="2387" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2387" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C2387" t="str">
         <f>C2306</f>
@@ -34021,7 +34021,7 @@
     </row>
     <row r="2391" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C2391" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G2391">
         <f>(G2387*ASSUMPTIONS!G7)/'rough sheet'!G2386</f>
@@ -34038,7 +34038,7 @@
     </row>
     <row r="2392" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C2392" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G2392" s="88">
         <f>G2391/G749</f>
@@ -34127,7 +34127,7 @@
     </row>
     <row r="2398" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C2398" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F2398">
         <f>F2399*F2387*F2404</f>
@@ -34136,7 +34136,7 @@
     </row>
     <row r="2399" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C2399" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F2399" s="60">
         <f>F2400/F2401</f>
@@ -34145,7 +34145,7 @@
     </row>
     <row r="2400" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C2400" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F2400">
         <v>29.5</v>
@@ -34153,7 +34153,7 @@
     </row>
     <row r="2401" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2401" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F2401">
         <v>858.5</v>
@@ -34161,12 +34161,12 @@
     </row>
     <row r="2403" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2403" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="2404" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2404" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F2404" s="11">
         <v>0.85</v>
@@ -34174,17 +34174,17 @@
     </row>
     <row r="2406" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2406" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="2407" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2407" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="2411" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2411" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="2412" spans="3:10" x14ac:dyDescent="0.3">
@@ -34284,20 +34284,20 @@
     </row>
     <row r="2421" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C2421" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="2422" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C2422" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="2423" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2423" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C2423" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F2423">
         <f>AVERAGE(E2412:F2412)</f>
@@ -34397,7 +34397,7 @@
     </row>
     <row r="2427" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C2427" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G2427" s="88">
         <f>G2426/G749</f>
@@ -34440,7 +34440,7 @@
         <v>other trade  receivables(net of allowance)</v>
       </c>
       <c r="D2430" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E2430">
         <f>E2312</f>
@@ -34495,7 +34495,7 @@
         <v>prepayments</v>
       </c>
       <c r="D2432" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E2432">
         <f>E2313</f>
@@ -34550,7 +34550,7 @@
         <v>other debtors</v>
       </c>
       <c r="D2434" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E2434">
         <f>E2314</f>
@@ -34605,7 +34605,7 @@
         <v>Amount due from associates and joint ventures</v>
       </c>
       <c r="D2436" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E2436">
         <f>E2315</f>
@@ -34724,7 +34724,7 @@
     </row>
     <row r="2440" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2440" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E2440" s="60">
         <f>E2438/'HISTORICAL FS'!E12</f>
@@ -34753,7 +34753,7 @@
     </row>
     <row r="2441" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2441" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E2441" s="95">
         <f>(E2440)*ASSUMPTIONS!E7</f>
@@ -34805,7 +34805,7 @@
     </row>
     <row r="2445" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2445" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2446" spans="3:14" x14ac:dyDescent="0.3">
@@ -34836,10 +34836,10 @@
     </row>
     <row r="2447" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2447" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D2447" t="s">
         <v>1026</v>
-      </c>
-      <c r="D2447" t="s">
-        <v>1027</v>
       </c>
       <c r="E2447">
         <f>(E2446/'HISTORICAL FS'!E13)*ASSUMPTIONS!E7</f>
@@ -34914,7 +34914,7 @@
     </row>
     <row r="2449" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2449" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="2450" spans="2:10" x14ac:dyDescent="0.3">
@@ -34945,10 +34945,10 @@
     </row>
     <row r="2452" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2452" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D2452" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E2452" s="88">
         <f>E2450/E2446</f>
@@ -34977,12 +34977,12 @@
     </row>
     <row r="2454" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2454" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="2455" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2455" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E2455" s="2">
         <f>E2258</f>
@@ -35007,7 +35007,7 @@
     </row>
     <row r="2456" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2456" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E2456">
         <v>275.39999999999998</v>
@@ -35027,7 +35027,7 @@
     </row>
     <row r="2457" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2457" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E2457">
         <v>0.5</v>
@@ -35047,7 +35047,7 @@
     </row>
     <row r="2458" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2458" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E2458">
         <v>4.8</v>
@@ -35067,7 +35067,7 @@
     </row>
     <row r="2459" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2459" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E2459">
         <v>76.8</v>
@@ -35087,7 +35087,7 @@
     </row>
     <row r="2460" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2460" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E2460">
         <v>79.5</v>
@@ -35107,7 +35107,7 @@
     </row>
     <row r="2461" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2461" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E2461">
         <v>0.2</v>
@@ -35124,7 +35124,7 @@
     </row>
     <row r="2462" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2462" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2462">
         <v>359.9</v>
@@ -35135,7 +35135,7 @@
     </row>
     <row r="2463" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2463" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2463">
         <v>81.2</v>
@@ -35146,7 +35146,7 @@
     </row>
     <row r="2464" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C2464" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E2464">
         <v>361.2</v>
@@ -35190,7 +35190,7 @@
     </row>
     <row r="2466" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2466" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E2466" s="2"/>
       <c r="F2466" s="2"/>
@@ -35200,7 +35200,7 @@
     </row>
     <row r="2467" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2467" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E2467" s="2"/>
       <c r="F2467" s="2">
@@ -35218,7 +35218,7 @@
     </row>
     <row r="2468" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2468" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="2470" spans="3:14" x14ac:dyDescent="0.3">
@@ -35227,7 +35227,7 @@
         <v xml:space="preserve">Trade payables </v>
       </c>
       <c r="D2470" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E2470" s="99">
         <f>(E2456/'HISTORICAL FS'!E13)*ASSUMPTIONS!E7</f>
@@ -35276,7 +35276,7 @@
         <v>Amounts owed to associates and JV</v>
       </c>
       <c r="D2471" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E2471" s="60">
         <f>E2457/'HISTORICAL FS'!E13</f>
@@ -35325,7 +35325,7 @@
         <v>Refund liabilities</v>
       </c>
       <c r="D2472" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E2472" s="71">
         <f>E2458/E2446</f>
@@ -35405,7 +35405,7 @@
         <v>Other taxation and social security</v>
       </c>
       <c r="D2474" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E2474" s="60">
         <f>E2459/E2516</f>
@@ -35438,7 +35438,7 @@
         <v>Deferred revenue from the sale of gift cards</v>
       </c>
       <c r="D2475" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E2475" s="60">
         <f>E2460/'HISTORICAL FS'!E12</f>
@@ -35499,7 +35499,7 @@
     </row>
     <row r="2482" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2482" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E2482">
         <v>99.1</v>
@@ -35519,7 +35519,7 @@
     </row>
     <row r="2483" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2483" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E2483">
         <v>82.7</v>
@@ -35539,7 +35539,7 @@
     </row>
     <row r="2484" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2484" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F2484">
         <v>29</v>
@@ -35560,7 +35560,7 @@
     </row>
     <row r="2485" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2485" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F2485">
         <v>17.3</v>
@@ -35577,7 +35577,7 @@
     </row>
     <row r="2486" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2486" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F2486">
         <v>14.6</v>
@@ -35636,10 +35636,10 @@
     </row>
     <row r="2488" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2488" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D2488" t="s">
         <v>1015</v>
-      </c>
-      <c r="D2488" t="s">
-        <v>1016</v>
       </c>
       <c r="E2488" s="2">
         <f>E2464-E2487</f>
@@ -35675,12 +35675,12 @@
     </row>
     <row r="2490" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2490" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="2491" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2491" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E2491">
         <v>4.7</v>
@@ -35688,7 +35688,7 @@
     </row>
     <row r="2493" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2493" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E2493">
         <v>795.2</v>
@@ -35718,7 +35718,7 @@
         <v>staff related accruals</v>
       </c>
       <c r="D2497" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E2497" s="60">
         <f>E2482/E2516</f>
@@ -35751,7 +35751,7 @@
         <v>warehouse and duty related accruals</v>
       </c>
       <c r="D2498" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E2498" s="60">
         <f>E2483/'HISTORICAL FS'!E13</f>
@@ -35784,7 +35784,7 @@
         <v>property accruals</v>
       </c>
       <c r="D2499" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="J2499">
         <v>37.85</v>
@@ -35796,7 +35796,7 @@
         <v>marketing accruals</v>
       </c>
       <c r="D2500" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E2500" s="60">
         <f>E2485/'HISTORICAL FS'!E12</f>
@@ -35856,7 +35856,7 @@
     </row>
     <row r="2505" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2505" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C2505" t="str">
         <f>'HISTORICAL FS'!C135</f>
@@ -35885,7 +35885,7 @@
     </row>
     <row r="2506" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2506" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C2506" t="str">
         <f>'HISTORICAL FS'!C145</f>
@@ -35914,10 +35914,10 @@
     </row>
     <row r="2508" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2508" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C2508" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="I2508">
         <v>713.6</v>
@@ -35925,12 +35925,12 @@
     </row>
     <row r="2509" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2509" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="2510" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2510" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="I2510">
         <v>113.6</v>
@@ -35938,7 +35938,7 @@
     </row>
     <row r="2511" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2511" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="I2511">
         <v>300</v>
@@ -35951,10 +35951,10 @@
     </row>
     <row r="2513" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2513" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D2513" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="J2513">
         <f>(I2511+I2512)/I2508</f>
@@ -35967,7 +35967,7 @@
     </row>
     <row r="2516" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2516" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E2516">
         <v>703.2</v>
@@ -36012,7 +36012,7 @@
     </row>
     <row r="2519" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2519" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E2519" s="60">
         <f>E2516/'HISTORICAL FS'!E12</f>
@@ -36041,7 +36041,7 @@
     </row>
     <row r="2523" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2523" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="2524" spans="3:12" x14ac:dyDescent="0.3">
@@ -36051,7 +36051,7 @@
     </row>
     <row r="2525" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2525" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E2525">
         <v>123.2</v>
@@ -36071,7 +36071,7 @@
     </row>
     <row r="2526" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2526" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E2526">
         <v>11.6</v>
@@ -36091,7 +36091,7 @@
     </row>
     <row r="2527" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2527" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E2527" s="47">
         <f>E2525+E2526</f>
@@ -36134,7 +36134,7 @@
     </row>
     <row r="2529" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2529" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E2529" s="103">
         <f>E2527/E2550</f>
@@ -36186,12 +36186,12 @@
     </row>
     <row r="2531" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2531" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2532" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2532" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E2532">
         <v>20.7</v>
@@ -36215,7 +36215,7 @@
     </row>
     <row r="2533" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2533" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E2533">
         <v>-9.9</v>
@@ -36235,7 +36235,7 @@
     </row>
     <row r="2534" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2534" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E2534" s="47">
         <f>SUM(E2532:E2533)</f>
@@ -36278,7 +36278,7 @@
     </row>
     <row r="2536" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2536" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E2536" s="61">
         <f>E2534/E2550</f>
@@ -36324,7 +36324,7 @@
     </row>
     <row r="2538" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2538" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E2538" s="2">
         <f>E2534+E2527</f>
@@ -36349,12 +36349,12 @@
     </row>
     <row r="2541" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2541" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="2542" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2542" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C2542" t="str">
         <f>C964</f>
@@ -36398,7 +36398,7 @@
     </row>
     <row r="2543" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2543" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C2543" t="str">
         <f>C973</f>
@@ -36471,7 +36471,7 @@
     </row>
     <row r="2546" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2546" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C2546" t="str">
         <f>C996</f>
@@ -36500,7 +36500,7 @@
     </row>
     <row r="2549" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2549" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="2550" spans="1:9" x14ac:dyDescent="0.3">
@@ -36579,7 +36579,7 @@
     </row>
     <row r="2555" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2555" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C2555" t="s">
         <v>460</v>
@@ -36625,7 +36625,7 @@
     </row>
     <row r="2558" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2558" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C2558" t="s">
         <v>182</v>
@@ -36648,7 +36648,7 @@
     </row>
     <row r="2560" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2560" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E2560">
         <v>-13</v>
@@ -36668,7 +36668,7 @@
     </row>
     <row r="2561" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2561" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E2561">
         <v>34</v>
@@ -36688,7 +36688,7 @@
     </row>
     <row r="2563" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2563" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E2563">
         <v>134.80000000000001</v>
@@ -36708,7 +36708,7 @@
     </row>
     <row r="2564" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2564" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E2564">
         <v>10.799999999999999</v>
@@ -36728,7 +36728,7 @@
     </row>
     <row r="2569" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2569" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F2569">
         <f>E2573</f>
@@ -36737,7 +36737,7 @@
     </row>
     <row r="2570" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2570" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E2570">
         <f>E2550</f>
@@ -36777,7 +36777,7 @@
     </row>
     <row r="2571" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2571" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E2571">
         <v>21.7</v>
@@ -36797,7 +36797,7 @@
     </row>
     <row r="2572" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2572" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E2572">
         <f>-'HISTORICAL FS'!E63</f>
@@ -36841,7 +36841,7 @@
     </row>
     <row r="2573" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2573" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E2573">
         <f>E2560</f>
@@ -36866,7 +36866,7 @@
     </row>
     <row r="2576" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2576" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E2576" s="71">
         <f t="shared" ref="E2576:J2576" si="37">E2572/E2570</f>
@@ -36911,7 +36911,7 @@
     </row>
     <row r="2577" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2577" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F2577" s="60">
         <f>F2572/E2572-1</f>
@@ -36937,7 +36937,7 @@
     </row>
     <row r="2578" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2578" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F2578" s="60">
         <f t="shared" ref="F2578:N2578" si="38">F2570/E2570-1</f>
@@ -36984,7 +36984,7 @@
     </row>
     <row r="2582" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2582" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="I2582" s="10">
         <v>0.95199999999999996</v>
@@ -36998,7 +36998,7 @@
     </row>
     <row r="2583" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2583" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="I2583" s="10">
         <v>4.8000000000000001E-2</v>
@@ -37024,7 +37024,7 @@
     </row>
     <row r="2585" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2585" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="J2585" s="11">
         <v>0.25</v>
@@ -37032,7 +37032,7 @@
     </row>
     <row r="2587" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2587" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="J2587">
         <f>J2584/J2585</f>
@@ -37041,17 +37041,17 @@
     </row>
     <row r="2592" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2592" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="2594" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B2594" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="2595" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2595" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="E2595">
         <v>184</v>
@@ -37071,7 +37071,7 @@
     </row>
     <row r="2596" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2596" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F2596">
         <v>3.4</v>
@@ -37085,7 +37085,7 @@
     </row>
     <row r="2597" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2597" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F2597">
         <v>7.4</v>
@@ -37099,7 +37099,7 @@
     </row>
     <row r="2598" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2598" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F2598">
         <v>31.1</v>
@@ -37110,7 +37110,7 @@
     </row>
     <row r="2599" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2599" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E2599">
         <v>-4.4000000000000004</v>
@@ -37130,7 +37130,7 @@
     </row>
     <row r="2600" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2600" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E2600">
         <f>SUM(E2595:E2599)</f>
@@ -37192,7 +37192,7 @@
     </row>
     <row r="2606" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2606" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E2606" s="60">
         <f>-E1681/'HISTORICAL FS'!E12</f>
@@ -37241,17 +37241,17 @@
     </row>
     <row r="2607" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2607" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="2608" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2608" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="2611" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2611" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F2611" s="60">
         <f>F1699/E958</f>
@@ -37292,7 +37292,7 @@
     </row>
     <row r="2612" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2612" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F2612" s="60">
         <f>F1922/E960</f>
@@ -37820,7 +37820,7 @@
     </row>
     <row r="2642" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2642" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E2642">
         <f>E2650+E2625</f>
@@ -38329,7 +38329,7 @@
     </row>
     <row r="2672" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2672" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E2672">
         <f>E2667+E1792</f>
@@ -38359,7 +38359,7 @@
     </row>
     <row r="2676" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C2676" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F2676" s="60">
         <f>F2645/E958</f>
@@ -38384,7 +38384,7 @@
     </row>
     <row r="2677" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C2677" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F2677" s="60">
         <f>F2646/E960</f>
@@ -38414,7 +38414,7 @@
     </row>
     <row r="2680" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C2680" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F2680" s="60">
         <f>F2681/E959</f>
@@ -38466,7 +38466,7 @@
     </row>
     <row r="2684" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C2684" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F2684" s="60">
         <f>F2650/E2174</f>
@@ -38491,7 +38491,7 @@
     </row>
     <row r="2685" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C2685" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F2685" s="60">
         <f>F2185/(E2175+E2176)</f>
@@ -38516,7 +38516,7 @@
     </row>
     <row r="2687" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C2687" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="J2687">
         <f>J2685*(I2175+I2176)</f>
@@ -38525,7 +38525,7 @@
     </row>
     <row r="2689" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2689" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="2690" spans="3:12" x14ac:dyDescent="0.3">
@@ -38629,7 +38629,7 @@
     </row>
     <row r="2695" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2695" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="E2695">
         <f>E2197</f>
@@ -38676,7 +38676,7 @@
     </row>
     <row r="2698" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2698" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E2698" s="2">
         <f>-(E893+E896)</f>
@@ -38710,7 +38710,7 @@
     </row>
     <row r="2700" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2700" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E2700" s="60">
         <f>E2691/E2692</f>
@@ -38739,7 +38739,7 @@
     </row>
     <row r="2701" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C2701" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E2701" s="60">
         <f>E2690/E2692</f>
@@ -38846,7 +38846,7 @@
     </row>
     <row r="2707" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2707" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E2707" s="60">
         <f>E2706/'HISTORICAL FS'!E12</f>
@@ -38875,7 +38875,7 @@
     </row>
     <row r="2710" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2710" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E2710">
         <f>E2177</f>
@@ -38900,7 +38900,7 @@
     </row>
     <row r="2711" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2711" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="E2711">
         <f>E2174</f>
@@ -38925,7 +38925,7 @@
     </row>
     <row r="2712" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2712" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E2712" s="88">
         <f>E2711/E2710</f>
@@ -38979,7 +38979,7 @@
     </row>
     <row r="2714" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2714" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="E2714" s="60">
         <f>E2713/E2710</f>
@@ -39318,7 +39318,7 @@
     </row>
     <row r="2731" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2731" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="2732" spans="3:9" x14ac:dyDescent="0.3">
@@ -39333,20 +39333,20 @@
     </row>
     <row r="2734" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2734" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="2735" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C2735" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I2735" t="s">
         <v>1118</v>
-      </c>
-      <c r="I2735" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="2737" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2737" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F2737">
         <f>E2740</f>
@@ -39371,7 +39371,7 @@
     </row>
     <row r="2738" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2738" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G2738">
         <v>0.1</v>
@@ -39379,7 +39379,7 @@
     </row>
     <row r="2739" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2739" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="F2739">
         <v>0.4</v>
@@ -39439,20 +39439,20 @@
     </row>
     <row r="2742" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B2742" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="2743" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2743" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I2743" t="s">
         <v>1122</v>
-      </c>
-      <c r="I2743" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="2745" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2745" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="I2745">
         <v>440.8</v>
@@ -39460,7 +39460,7 @@
     </row>
     <row r="2746" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2746" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="I2746">
         <v>440.8</v>
@@ -39490,7 +39490,7 @@
     </row>
     <row r="2749" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2749" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E2749" t="str">
         <f t="shared" ref="E2749:J2749" si="52">E2761</f>
@@ -39519,12 +39519,12 @@
     </row>
     <row r="2750" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2750" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="2751" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2751" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E2751" t="str">
         <f t="shared" ref="E2751:J2751" si="53">E2749</f>
@@ -39553,7 +39553,7 @@
     </row>
     <row r="2752" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C2752" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E2752">
         <f t="shared" ref="E2752:J2752" si="54">E2757</f>
@@ -39582,12 +39582,12 @@
     </row>
     <row r="2753" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2753" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="2755" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2755" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="2757" spans="3:14" x14ac:dyDescent="0.3">
@@ -39658,7 +39658,7 @@
     </row>
     <row r="2759" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2759" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E2759">
         <f>E2757</f>
@@ -39687,7 +39687,7 @@
     </row>
     <row r="2760" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2760" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E2760">
         <v>73.900000000000006</v>
@@ -39726,10 +39726,10 @@
     </row>
     <row r="2761" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2761" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E2761" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F2761">
         <v>3.5</v>
@@ -39781,7 +39781,7 @@
     </row>
     <row r="2764" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2764" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="I2764">
         <v>990.7</v>
@@ -39796,7 +39796,7 @@
     </row>
     <row r="2765" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2765" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="J2765">
         <f>I2747</f>
@@ -39805,7 +39805,7 @@
     </row>
     <row r="2766" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2766" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="J2766">
         <f>J2761</f>
@@ -39876,7 +39876,7 @@
     </row>
     <row r="2774" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2774" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="J2774">
         <f>I2777</f>
@@ -39885,12 +39885,12 @@
     </row>
     <row r="2775" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2775" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="2776" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2776" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="J2776">
         <f>J2769</f>
@@ -39908,7 +39908,7 @@
     </row>
     <row r="2782" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2782" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E2782">
         <f>E889</f>
@@ -39933,7 +39933,7 @@
     </row>
     <row r="2783" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2783" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E2783">
         <f t="shared" ref="E2783:J2783" si="56">-(E893+E896)</f>
@@ -39962,7 +39962,7 @@
     </row>
     <row r="2784" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2784" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="E2784">
         <f>-E934</f>
@@ -39987,7 +39987,7 @@
     </row>
     <row r="2785" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2785" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E2785" s="47">
         <f>E2782-E2783-E2784</f>
@@ -40066,7 +40066,7 @@
     </row>
     <row r="2787" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2787" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="E2787" s="60">
         <f>-E2759/E2785</f>
@@ -40155,12 +40155,12 @@
     </row>
     <row r="2795" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2795" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="2796" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2796" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="J2796">
         <f>-I2799</f>
@@ -40169,7 +40169,7 @@
     </row>
     <row r="2797" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2797" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="I2797">
         <v>169</v>
@@ -40181,7 +40181,7 @@
     </row>
     <row r="2798" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2798" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="I2798">
         <v>154.30000000000001</v>
@@ -40196,7 +40196,7 @@
     </row>
     <row r="2799" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2799" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="I2799">
         <f>I2722</f>
@@ -40356,7 +40356,7 @@
     </row>
     <row r="2811" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2811" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F2811" s="60">
         <f>F2810/E2810-1</f>
@@ -40377,7 +40377,7 @@
     </row>
     <row r="2813" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2813" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="2814" spans="3:14" x14ac:dyDescent="0.3">
@@ -40492,7 +40492,7 @@
     </row>
     <row r="2819" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2819" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G2819" s="60">
         <f>G2816/F2816-1</f>
@@ -40521,12 +40521,12 @@
     </row>
     <row r="2821" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2821" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="2822" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2822" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J2822">
         <f>I2826</f>
@@ -40551,7 +40551,7 @@
     </row>
     <row r="2823" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2823" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="I2823">
         <f t="shared" ref="I2823:N2823" si="57">I2816</f>
@@ -40580,7 +40580,7 @@
     </row>
     <row r="2824" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2824" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="I2824">
         <v>1.5</v>
@@ -40608,7 +40608,7 @@
     </row>
     <row r="2825" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2825" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="I2825">
         <v>8</v>
@@ -40635,7 +40635,7 @@
     </row>
     <row r="2826" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2826" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="I2826">
         <f>I2729</f>
@@ -40664,7 +40664,7 @@
     </row>
     <row r="2828" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2828" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="E2828">
         <v>0</v>
@@ -40684,7 +40684,7 @@
     </row>
     <row r="2829" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2829" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="J2829" s="60">
         <v>0.182592592592593</v>
@@ -40704,7 +40704,7 @@
     </row>
     <row r="2830" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2830" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="J2830">
         <v>8</v>
@@ -40712,7 +40712,7 @@
     </row>
     <row r="2831" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C2831" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="J2831">
         <v>1.5</v>
@@ -40720,7 +40720,7 @@
     </row>
     <row r="2834" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2834" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="2835" spans="1:14" x14ac:dyDescent="0.3">
@@ -40730,7 +40730,7 @@
     </row>
     <row r="2836" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2836" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C2836" t="str">
         <f>C981</f>
@@ -40759,7 +40759,7 @@
     </row>
     <row r="2837" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2837" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C2837" t="str">
         <f>'HISTORICAL FS'!C145</f>
@@ -40862,12 +40862,12 @@
     </row>
     <row r="2845" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2845" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="2846" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2846" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E2846">
         <v>18.600000000000001</v>
@@ -40911,7 +40911,7 @@
     </row>
     <row r="2847" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2847" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G2847">
         <v>13.1</v>
@@ -40934,7 +40934,7 @@
     </row>
     <row r="2848" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2848" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E2848">
         <v>4.3</v>
@@ -40974,7 +40974,7 @@
     </row>
     <row r="2849" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2849" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E2849">
         <v>-1.4</v>
@@ -41014,7 +41014,7 @@
     </row>
     <row r="2850" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2850" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G2850">
         <v>-0.1</v>
@@ -41043,7 +41043,7 @@
     </row>
     <row r="2851" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2851" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E2851">
         <v>0.4</v>
@@ -41083,7 +41083,7 @@
     </row>
     <row r="2852" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2852" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E2852" s="47">
         <f>SUM(E2846:E2851)</f>
@@ -41189,12 +41189,12 @@
     </row>
     <row r="2861" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2861" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="2862" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2862" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C2862" t="str">
         <f>C983</f>
@@ -41223,7 +41223,7 @@
     </row>
     <row r="2863" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2863" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C2863" t="str">
         <f>C993</f>
@@ -41363,7 +41363,7 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="205" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -41684,7 +41684,7 @@
         <v>Revenue</v>
       </c>
       <c r="D8" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G8">
         <f>'MODEL&amp;SCHEDULE'!G17</f>
@@ -41721,10 +41721,10 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="C9" s="167" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D9" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G9" s="71"/>
       <c r="H9" s="70">
@@ -41767,7 +41767,7 @@
         <v xml:space="preserve"> EBITDA</v>
       </c>
       <c r="D13" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G13" s="99">
         <f>'MODEL&amp;SCHEDULE'!G67</f>
@@ -41804,10 +41804,10 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="C14" s="167" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D14" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G14" s="167"/>
       <c r="H14" s="70">
@@ -41845,7 +41845,7 @@
         <v>EBITDA margin</v>
       </c>
       <c r="D15" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G15" s="197">
         <f>'MODEL&amp;SCHEDULE'!G78</f>
@@ -41904,7 +41904,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C18" s="167"/>
       <c r="G18" s="167"/>
@@ -41922,7 +41922,7 @@
         <v xml:space="preserve"> EBIT</v>
       </c>
       <c r="D19" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G19" s="195">
         <f>'MODEL&amp;SCHEDULE'!G64</f>
@@ -41959,10 +41959,10 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C20" s="167" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D20" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G20" s="167"/>
       <c r="H20" s="70">
@@ -42000,7 +42000,7 @@
         <v>EBIT margin</v>
       </c>
       <c r="D21" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G21" s="197">
         <f>'MODEL&amp;SCHEDULE'!G77</f>
@@ -42059,7 +42059,7 @@
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C24" s="167"/>
       <c r="G24" s="167"/>
@@ -42077,7 +42077,7 @@
         <v>EBIAT/NOPAT</v>
       </c>
       <c r="D25" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G25" s="167">
         <f>'MODEL&amp;SCHEDULE'!G73</f>
@@ -42114,10 +42114,10 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C26" s="167" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D26" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G26" s="167"/>
       <c r="H26" s="70">
@@ -42155,7 +42155,7 @@
         <v>EBIAT/NOPAT margin</v>
       </c>
       <c r="D27" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G27" s="203">
         <f>'MODEL&amp;SCHEDULE'!G79</f>
@@ -42198,7 +42198,7 @@
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.3">
@@ -42207,7 +42207,7 @@
         <v>Recurring Net Income</v>
       </c>
       <c r="D32" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G32" s="100">
         <f>'MODEL&amp;SCHEDULE'!G71</f>
@@ -42244,10 +42244,10 @@
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C33" s="167" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="D33" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H33" s="70">
         <f>IFERROR(H32/G32-1,0)</f>
@@ -42284,7 +42284,7 @@
         <v>Recurring NI margin</v>
       </c>
       <c r="D34" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H34" s="197">
         <f>'MODEL&amp;SCHEDULE'!H84</f>
@@ -42317,7 +42317,7 @@
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.3">
@@ -42914,7 +42914,7 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -43324,7 +43324,7 @@
     </row>
     <row r="29" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C29" s="41" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="E29" s="47">
         <f>SUM(E27:E28)</f>
@@ -46740,7 +46740,7 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E7">
         <f>DATE(E5,12,31)-DATE(E5,1,1)+1</f>
@@ -46785,7 +46785,7 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D8" s="40">
         <v>1000000</v>
@@ -46793,7 +46793,7 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D9" s="40">
         <v>0.1</v>
@@ -46801,7 +46801,7 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D10" s="40">
         <v>12</v>
@@ -46822,7 +46822,7 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D14" s="11">
         <v>0.1</v>
@@ -46833,7 +46833,7 @@
         <v>103</v>
       </c>
       <c r="D15" s="82" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
@@ -46849,12 +46849,12 @@
         <v>7</v>
       </c>
       <c r="D17" s="83" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D18" s="84" t="s">
         <v>9</v>
@@ -46865,12 +46865,12 @@
         <v>96</v>
       </c>
       <c r="D19" s="85" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D20" s="80">
         <v>10</v>
@@ -46949,7 +46949,7 @@
     </row>
     <row r="36" spans="1:33" ht="18" x14ac:dyDescent="0.35">
       <c r="A36" s="62" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B36" s="135"/>
       <c r="C36" s="135"/>
@@ -47001,7 +47001,7 @@
         <v>Online UK</v>
       </c>
       <c r="D39" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="97">
@@ -47026,7 +47026,7 @@
         <v>Online (International)</v>
       </c>
       <c r="D40" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="97">
@@ -47058,7 +47058,7 @@
         <v>Retail stores</v>
       </c>
       <c r="D42" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
@@ -47086,7 +47086,7 @@
         <v>Next Finance/credit account interest</v>
       </c>
       <c r="D43" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
@@ -47114,7 +47114,7 @@
         <v>Total Platform +next sale of investment</v>
       </c>
       <c r="D44" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
@@ -47142,7 +47142,7 @@
         <v>Other business Activities</v>
       </c>
       <c r="D45" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="10"/>
@@ -47184,10 +47184,10 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D48" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="10"/>
@@ -47227,10 +47227,10 @@
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C55" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D55" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J55" s="97">
         <v>0.56086810280947685</v>
@@ -47241,7 +47241,7 @@
         <v>19</v>
       </c>
       <c r="D56" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J56" s="97">
         <v>0.43451257738323135</v>
@@ -47252,7 +47252,7 @@
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J57" s="97">
         <v>0.14720635225363063</v>
@@ -47263,7 +47263,7 @@
         <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J58" s="97">
         <v>0.10297190707447981</v>
@@ -47271,23 +47271,23 @@
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D59" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C63" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D63" t="s">
         <v>1345</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1346</v>
       </c>
       <c r="J63" s="93">
         <v>0.25</v>
@@ -47295,10 +47295,10 @@
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="D64" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J64" s="97">
         <v>0.95177552145280464</v>
@@ -47306,10 +47306,10 @@
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C65" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D65" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J65" s="97">
         <v>4.8224478547195443E-2</v>
@@ -47317,10 +47317,10 @@
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D66" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E66" s="60"/>
       <c r="F66" s="60"/>
@@ -47333,10 +47333,10 @@
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D67" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J67" s="81">
         <v>265</v>
@@ -47344,10 +47344,10 @@
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D68" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J68" s="81">
         <v>5.378973105134488E-2</v>
@@ -47355,7 +47355,7 @@
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C69" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="J69" s="81">
         <v>5.7997423256263101</v>
@@ -47375,7 +47375,7 @@
     </row>
     <row r="71" spans="1:33" ht="18" x14ac:dyDescent="0.35">
       <c r="A71" s="62" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B71" s="135"/>
       <c r="C71" s="135"/>
@@ -47420,7 +47420,7 @@
         <v>22</v>
       </c>
       <c r="D74" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="J74" s="94">
         <v>170.23890879887563</v>
@@ -47443,7 +47443,7 @@
         <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="J75" s="81">
         <v>99.534975003583199</v>
@@ -47466,7 +47466,7 @@
         <v>24</v>
       </c>
       <c r="D76" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="J76" s="81">
         <v>34.747341136293144</v>
@@ -47486,17 +47486,17 @@
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C77" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C78" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C79" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="J79" s="81">
         <v>75</v>
@@ -47504,15 +47504,15 @@
     </row>
     <row r="81" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C81" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="82" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D82" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J82" s="81">
         <v>1323</v>
@@ -47520,10 +47520,10 @@
     </row>
     <row r="83" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C83" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D83" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J83" s="81">
         <v>3.3086987601475985E-2</v>
@@ -47531,7 +47531,7 @@
     </row>
     <row r="84" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C84" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="J84" s="81">
         <v>12.083394073154651</v>
@@ -47542,7 +47542,7 @@
         <v>480</v>
       </c>
       <c r="D85" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J85" s="97">
         <v>1.0609932951226135E-2</v>
@@ -47553,7 +47553,7 @@
         <v>476</v>
       </c>
       <c r="D86" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J86" s="97">
         <v>1.1269230432004947E-2</v>
@@ -47564,7 +47564,7 @@
         <v>477</v>
       </c>
       <c r="D87" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J87" s="97">
         <v>7.3463443048772756E-3</v>
@@ -47575,7 +47575,7 @@
         <v>478</v>
       </c>
       <c r="D88" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J88" s="97">
         <v>3.8614799133676269E-3</v>
@@ -47583,10 +47583,10 @@
     </row>
     <row r="90" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C90" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D90" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J90" s="97">
         <v>3.9996575633742447E-2</v>
@@ -47594,15 +47594,15 @@
     </row>
     <row r="92" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C92" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="93" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C93" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D93" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="J93" s="81">
         <v>34.747341136293144</v>
@@ -47622,10 +47622,10 @@
     </row>
     <row r="94" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C94" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D94" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J94" s="97">
         <v>5.0127147936132599E-4</v>
@@ -47633,10 +47633,10 @@
     </row>
     <row r="95" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D95" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J95" s="97">
         <v>7.1301750162105063E-2</v>
@@ -47656,10 +47656,10 @@
     </row>
     <row r="97" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C97" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D97" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J97" s="97">
         <v>0.12189371929556898</v>
@@ -47667,10 +47667,10 @@
     </row>
     <row r="98" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C98" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D98" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J98" s="97">
         <v>1.7223598139482495E-2</v>
@@ -47678,10 +47678,10 @@
     </row>
     <row r="99" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C99" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D99" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J99" s="81">
         <v>0.2</v>
@@ -47689,15 +47689,15 @@
     </row>
     <row r="101" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C101" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="102" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C102" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D102" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J102" s="97">
         <v>8.612861556647762E-2</v>
@@ -47705,10 +47705,10 @@
     </row>
     <row r="103" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C103" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D103" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J103" s="97">
         <v>3.3830800141696621E-2</v>
@@ -47716,10 +47716,10 @@
     </row>
     <row r="104" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C104" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D104" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J104" s="81">
         <v>37.85</v>
@@ -47727,10 +47727,10 @@
     </row>
     <row r="105" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C105" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D105" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J105" s="97">
         <v>2.13234766567641E-3</v>
@@ -47738,10 +47738,10 @@
     </row>
     <row r="106" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C106" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D106" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J106" s="81">
         <v>15.218609865470853</v>
@@ -47761,10 +47761,10 @@
     </row>
     <row r="107" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C107" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D107" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J107" s="81">
         <v>201.90000000000003</v>
@@ -47772,10 +47772,10 @@
     </row>
     <row r="109" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C109" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="D109" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J109" s="97">
         <v>0.15898882989487034</v>
@@ -47783,7 +47783,7 @@
     </row>
     <row r="113" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B113" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="114" spans="2:14" x14ac:dyDescent="0.3">
@@ -47791,7 +47791,7 @@
         <v>25</v>
       </c>
       <c r="D114" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="M114" s="97">
         <v>3.1621516782440101E-2</v>
@@ -47802,10 +47802,10 @@
     </row>
     <row r="115" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C115" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D115" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J115" s="81">
         <f>'rough sheet'!J1406</f>
@@ -47830,15 +47830,15 @@
     </row>
     <row r="117" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C117" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="118" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C118" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D118" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J118" s="97">
         <v>0.1627698806714972</v>
@@ -47846,10 +47846,10 @@
     </row>
     <row r="119" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C119" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D119" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J119" s="97">
         <v>0.1878653628545508</v>
@@ -47857,10 +47857,10 @@
     </row>
     <row r="120" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C120" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D120" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J120" s="97">
         <v>5.0972390647897395E-2</v>
@@ -47868,10 +47868,10 @@
     </row>
     <row r="121" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C121" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D121" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J121" s="97">
         <v>0.3656861860697353</v>
@@ -47879,10 +47879,10 @@
     </row>
     <row r="122" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C122" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D122" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J122" s="93">
         <v>0.13963822156717098</v>
@@ -47890,10 +47890,10 @@
     </row>
     <row r="123" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C123" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D123" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J123" s="97">
         <v>0.88946529018220666</v>
@@ -47901,7 +47901,7 @@
     </row>
     <row r="124" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C124" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="J124" s="97">
         <v>0.11053470981779333</v>
@@ -47909,15 +47909,15 @@
     </row>
     <row r="125" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C125" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="126" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C126" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D126" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J126" s="97">
         <v>0.82318758209737308</v>
@@ -47925,10 +47925,10 @@
     </row>
     <row r="127" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C127" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D127" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J127" s="97">
         <v>0.17681241790262681</v>
@@ -47936,15 +47936,15 @@
     </row>
     <row r="128" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C128" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C129" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D129" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J129" s="106">
         <v>1.2992682325098065E-2</v>
@@ -47955,15 +47955,15 @@
     </row>
     <row r="132" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C132" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C133" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D133" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J133" s="93">
         <v>0.16476540697802017</v>
@@ -47971,7 +47971,7 @@
     </row>
     <row r="134" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C134" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="J134" s="81">
         <v>0</v>
@@ -47979,28 +47979,28 @@
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B138" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B139" s="2"/>
       <c r="C139" s="116" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="D139" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B140" s="2"/>
       <c r="C140" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B141" s="2"/>
       <c r="C141" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D141" s="113">
         <v>3.6249999999999998E-2</v>
@@ -48009,7 +48009,7 @@
     <row r="142" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B142" s="2"/>
       <c r="C142" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D142" s="113">
         <v>0.05</v>
@@ -48022,13 +48022,13 @@
     <row r="144" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B144" s="2"/>
       <c r="C144" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="145" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B145" s="2"/>
       <c r="C145" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="146" spans="2:14" x14ac:dyDescent="0.3">
@@ -48036,15 +48036,15 @@
         <v>4.3749999999999997E-2</v>
       </c>
       <c r="C146" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D146" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="147" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C147" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D147" s="114">
         <v>3.7289999999999997E-2</v>
@@ -48052,7 +48052,7 @@
     </row>
     <row r="148" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C148" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D148" s="10">
         <v>1.7000000000000001E-2</v>
@@ -48071,16 +48071,16 @@
     <row r="151" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B151" s="2"/>
       <c r="C151" s="2" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="152" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B152" s="2"/>
       <c r="C152" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D152" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="I152" s="81">
         <v>112.9</v>
@@ -48089,10 +48089,10 @@
     <row r="153" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B153" s="2"/>
       <c r="C153" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D153" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="I153" s="81">
         <v>300</v>
@@ -48101,10 +48101,10 @@
     <row r="154" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B154" s="2"/>
       <c r="C154" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D154" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="I154" s="81">
         <v>300</v>
@@ -48122,10 +48122,10 @@
     <row r="157" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B157" s="2"/>
       <c r="C157" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D157" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J157" s="81">
         <f>-I152</f>
@@ -48150,10 +48150,10 @@
     <row r="158" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B158" s="2"/>
       <c r="C158" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D158" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J158" s="81">
         <v>0</v>
@@ -48175,10 +48175,10 @@
     <row r="159" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B159" s="2"/>
       <c r="C159" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D159" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J159" s="81">
         <v>0</v>
@@ -48208,7 +48208,7 @@
     <row r="163" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B163" s="2"/>
       <c r="C163" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="164" spans="2:12" x14ac:dyDescent="0.3">
@@ -48218,7 +48218,7 @@
         <v>Corporate bonds 4.375% repayable October 2026</v>
       </c>
       <c r="D164" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J164" s="81">
         <v>243</v>
@@ -48231,7 +48231,7 @@
         <v>Corporate bonds 3.625% repayable May 2028</v>
       </c>
       <c r="D165" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="L165" s="81">
         <v>107</v>
@@ -48252,15 +48252,15 @@
     </row>
     <row r="169" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C169" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="170" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C170" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D170" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E170" s="60"/>
       <c r="F170" s="60"/>
@@ -48273,7 +48273,7 @@
     </row>
     <row r="171" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C171" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E171" s="10"/>
     </row>
@@ -48282,7 +48282,7 @@
         <v>470</v>
       </c>
       <c r="D172" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="I172" s="81">
         <v>0.16813362672534504</v>
@@ -48290,10 +48290,10 @@
     </row>
     <row r="173" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C173" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D173" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="I173" s="81">
         <v>0.83186637327465496</v>
@@ -48305,20 +48305,20 @@
     <row r="176" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B176" s="2"/>
       <c r="C176" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B177" s="2"/>
       <c r="C177" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D177" s="81">
         <f>(2.15%+2.9%)/2</f>
         <v>2.5249999999999998E-2</v>
       </c>
       <c r="J177" s="81" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="178" spans="2:10" x14ac:dyDescent="0.3">
@@ -48327,13 +48327,13 @@
     <row r="179" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B179" s="2"/>
       <c r="C179" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B180" s="2"/>
       <c r="C180" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="D180" s="81">
         <v>3.7499999999999999E-2</v>
@@ -48342,7 +48342,7 @@
     <row r="181" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B181" s="2"/>
       <c r="C181" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="D181" s="81">
         <v>2.5000000000000001E-3</v>
@@ -48351,7 +48351,7 @@
     <row r="182" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B182" s="2"/>
       <c r="C182" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D182" s="81">
         <f>D180+D181</f>
@@ -48365,7 +48365,7 @@
     <row r="184" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B184" s="2"/>
       <c r="C184" s="2" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.3">
@@ -48382,7 +48382,7 @@
     <row r="186" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B186" s="2"/>
       <c r="C186" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D186" s="60">
         <v>0.01</v>
@@ -48403,7 +48403,7 @@
     <row r="189" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B189" s="2"/>
       <c r="C189" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="I189" s="81">
         <v>0.01</v>
@@ -48412,16 +48412,16 @@
     <row r="190" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B190" s="2"/>
       <c r="C190" s="2" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="191" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B191" s="2"/>
       <c r="C191" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D191" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J191" s="97">
         <v>0.51663201663201663</v>
@@ -48433,7 +48433,7 @@
     <row r="193" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B193" s="2"/>
       <c r="C193" s="2" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="194" spans="2:14" x14ac:dyDescent="0.3">
@@ -48456,7 +48456,7 @@
     <row r="197" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B197" s="2"/>
       <c r="C197" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="J197" s="97">
         <v>1.8919614275049811E-2</v>
@@ -48473,15 +48473,15 @@
     </row>
     <row r="203" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B203" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="204" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C204" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D204" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J204" s="107">
         <v>0.5</v>
@@ -48501,15 +48501,15 @@
     </row>
     <row r="205" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C205" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D205" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="206" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C206" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="J206" s="81">
         <v>324</v>
@@ -48529,7 +48529,7 @@
     </row>
     <row r="207" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C207" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="J207" s="81">
         <v>318</v>
@@ -48549,10 +48549,10 @@
     </row>
     <row r="208" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C208" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D208" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J208" s="81">
         <v>500</v>
@@ -48560,7 +48560,7 @@
     </row>
     <row r="209" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C209" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="J209" s="81">
         <v>0.36</v>
@@ -48578,7 +48578,7 @@
     </row>
     <row r="211" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C211" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="J211" s="81">
         <v>2.8</v>
@@ -48586,18 +48586,18 @@
     </row>
     <row r="212" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C212" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D212" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J212" s="81" t="s">
         <v>1148</v>
-      </c>
-      <c r="D212" t="s">
-        <v>1150</v>
-      </c>
-      <c r="J212" s="81" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="213" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C213" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="J213" s="112">
         <v>96</v>
@@ -48605,7 +48605,7 @@
     </row>
     <row r="214" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C214" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="J214" s="81">
         <v>-64</v>
@@ -48613,7 +48613,7 @@
     </row>
     <row r="215" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C215" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="J215" s="81">
         <v>105</v>
@@ -48621,12 +48621,12 @@
     </row>
     <row r="217" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C217" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="218" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C218" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="J218" s="81">
         <v>0.182592592592593</v>
@@ -48646,7 +48646,7 @@
     </row>
     <row r="219" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C219" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="J219" s="81">
         <v>8</v>
@@ -48666,7 +48666,7 @@
     </row>
     <row r="220" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C220" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="J220" s="81">
         <v>2</v>
@@ -48674,7 +48674,7 @@
     </row>
     <row r="224" spans="2:33" ht="18" x14ac:dyDescent="0.35">
       <c r="B224" s="152" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C224" s="135"/>
       <c r="D224" s="135"/>
@@ -48711,7 +48711,7 @@
     <row r="231" spans="2:33" ht="21" x14ac:dyDescent="0.4">
       <c r="B231" s="135"/>
       <c r="C231" s="150" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D231" s="135"/>
       <c r="E231" s="135"/>
@@ -48769,10 +48769,10 @@
     </row>
     <row r="234" spans="2:33" x14ac:dyDescent="0.3">
       <c r="C234" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D234" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J234" s="81">
         <v>4.5999999999999999E-2</v>
@@ -48811,7 +48811,7 @@
         <v>582</v>
       </c>
       <c r="D238" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J238" s="81">
         <v>4.4999999999999998E-2</v>
@@ -48838,7 +48838,7 @@
         <v>594</v>
       </c>
       <c r="D241" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J241" s="97">
         <v>-1.4999999999999999E-2</v>
@@ -48849,7 +48849,7 @@
         <v>583</v>
       </c>
       <c r="D242" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J242" s="97">
         <v>4.5999999999999999E-2</v>
@@ -48860,7 +48860,7 @@
         <v>585</v>
       </c>
       <c r="D243" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J243" s="97">
         <v>2.1999999999999999E-2</v>
@@ -48871,7 +48871,7 @@
         <v>586</v>
       </c>
       <c r="D244" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J244" s="97">
         <v>0.14299999999999999</v>
@@ -48882,7 +48882,7 @@
         <v>587</v>
       </c>
       <c r="D245" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J245" s="97">
         <v>4.8000000000000001E-2</v>
@@ -48893,7 +48893,7 @@
         <v>588</v>
       </c>
       <c r="D246" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J246" s="97">
         <v>-6.0000000000000001E-3</v>
@@ -48904,7 +48904,7 @@
         <v>394</v>
       </c>
       <c r="D247" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J247" s="97">
         <v>4.4999999999999998E-2</v>
@@ -48915,7 +48915,7 @@
         <v>602</v>
       </c>
       <c r="D249" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J249" s="97">
         <v>0.14299999999999999</v>
@@ -48926,7 +48926,7 @@
         <v>603</v>
       </c>
       <c r="D250" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="J250" s="97">
         <v>0.153</v>
@@ -49090,7 +49090,7 @@
     </row>
     <row r="290" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C290" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="K290" s="81">
         <f>'rough sheet'!K1458</f>
@@ -49123,7 +49123,7 @@
     </row>
     <row r="294" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C294" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="J294" s="81">
         <v>790</v>
@@ -49534,7 +49534,7 @@
     <row r="20" spans="2:26" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="135"/>
       <c r="C20" s="150" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="D20" s="135"/>
       <c r="E20" s="135"/>
@@ -49653,7 +49653,7 @@
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C29" s="147" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="J29" s="184" cm="1">
         <f t="array" ref="J29">INDEX(J31:J33,S_Scenario)</f>
@@ -49741,7 +49741,7 @@
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="147" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.3">
@@ -49834,7 +49834,7 @@
     </row>
     <row r="45" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C45" s="147" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="J45" s="184" cm="1">
         <f t="array" ref="J45">INDEX(J47:J49,S_Scenario)</f>
@@ -50013,7 +50013,7 @@
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C62" s="147" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="J62" s="184" cm="1">
         <f t="array" ref="J62">INDEX(J64:J66,S_Scenario)</f>
@@ -50131,7 +50131,7 @@
     </row>
     <row r="71" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C71" s="147" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J71" s="182" cm="1">
         <f t="array" ref="J71">INDEX(J73:J75,S_Scenario)</f>
@@ -50246,7 +50246,7 @@
     </row>
     <row r="79" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C79" s="147" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="J79" s="182" cm="1">
         <f t="array" ref="J79">INDEX(J81:J83,S_Scenario)</f>
@@ -50605,7 +50605,7 @@
         <v>Millions for the Year Ended January 31</v>
       </c>
       <c r="C6" s="212" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="D6" s="212"/>
       <c r="E6" s="212"/>
@@ -51950,7 +51950,7 @@
     <row r="47" spans="2:15" ht="18" x14ac:dyDescent="0.35">
       <c r="B47" s="156"/>
       <c r="C47" s="62" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -52014,7 +52014,7 @@
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B49" s="156" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C49" s="2"/>
       <c r="E49" s="2"/>
@@ -52316,7 +52316,7 @@
     <row r="56" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B56" s="156"/>
       <c r="C56" s="2" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="E56" s="47">
         <f>SUM(E54:E55)</f>
@@ -52633,7 +52633,7 @@
     <row r="64" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B64" s="156"/>
       <c r="C64" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="E64" s="46">
         <f>SUM(E59:E63)</f>
@@ -52689,7 +52689,7 @@
     <row r="66" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B66" s="156"/>
       <c r="C66" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="E66">
         <f>E810+E811</f>
@@ -52736,7 +52736,7 @@
     <row r="67" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B67" s="156"/>
       <c r="C67" s="2" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="E67" s="47">
         <f>E64+E66</f>
@@ -52813,7 +52813,7 @@
     <row r="70" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B70" s="156"/>
       <c r="C70" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="E70">
         <f>G816</f>
@@ -52860,7 +52860,7 @@
     <row r="71" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="156"/>
       <c r="C71" s="2" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="E71" s="191">
         <f>E56-E70</f>
@@ -52976,7 +52976,7 @@
         <v>303</v>
       </c>
       <c r="D77" s="48" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E77" s="194">
         <f>E64/E17</f>
@@ -53037,7 +53037,7 @@
         <v>304</v>
       </c>
       <c r="D78" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E78" s="159">
         <f>E67/E17</f>
@@ -53084,10 +53084,10 @@
     <row r="79" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B79" s="156"/>
       <c r="C79" s="167" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D79" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E79" s="159">
         <f>E73/E17</f>
@@ -53134,10 +53134,10 @@
     <row r="80" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B80" s="156"/>
       <c r="C80" s="167" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="D80" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E80" s="60">
         <f>E71/E17</f>
@@ -53184,10 +53184,10 @@
     <row r="81" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B81" s="156"/>
       <c r="C81" s="167" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D81" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F81" s="60">
         <f>F71/AVERAGE(E205:F205)</f>
@@ -53230,10 +53230,10 @@
     <row r="82" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B82" s="156"/>
       <c r="C82" s="167" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="D82" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E82" s="161"/>
       <c r="F82" s="161">
@@ -53276,7 +53276,7 @@
     </row>
     <row r="83" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B83" s="154" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Z83" s="52"/>
     </row>
@@ -53287,7 +53287,7 @@
         <v>Recurring NI margin</v>
       </c>
       <c r="D84" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E84" s="171"/>
       <c r="F84" s="171">
@@ -53331,10 +53331,10 @@
     <row r="85" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B85" s="156"/>
       <c r="C85" s="167" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="D85" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E85" s="160"/>
       <c r="F85" s="160">
@@ -53378,10 +53378,10 @@
     <row r="86" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B86" s="156"/>
       <c r="C86" s="167" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="D86" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E86" s="80"/>
       <c r="F86" s="80">
@@ -53425,10 +53425,10 @@
     <row r="87" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B87" s="156"/>
       <c r="C87" s="170" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="D87" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E87" s="161"/>
       <c r="F87" s="161">
@@ -53477,7 +53477,7 @@
     <row r="89" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B89" s="158"/>
       <c r="C89" s="149" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D89" s="135"/>
       <c r="E89" s="188">
@@ -54026,7 +54026,7 @@
     </row>
     <row r="105" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C105" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="J105" s="99">
         <f>J736+J737+J739</f>
@@ -54189,7 +54189,7 @@
     </row>
     <row r="109" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C109" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="J109" s="99"/>
       <c r="K109" s="99"/>
@@ -58047,7 +58047,7 @@
       <c r="A258" s="127"/>
       <c r="B258" s="127"/>
       <c r="C258" s="210" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D258" s="210"/>
       <c r="E258" s="210"/>
@@ -58095,7 +58095,7 @@
     </row>
     <row r="260" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C260" s="55" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D260" s="55"/>
       <c r="E260" s="55"/>
@@ -58216,7 +58216,7 @@
     </row>
     <row r="264" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C264" s="55" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="D264" s="96"/>
       <c r="E264" s="96"/>
@@ -58264,7 +58264,7 @@
     </row>
     <row r="266" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C266" s="55" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D266" s="55"/>
       <c r="E266" s="55"/>
@@ -58329,7 +58329,7 @@
     </row>
     <row r="269" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C269" s="55" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D269" s="96"/>
       <c r="E269" s="96"/>
@@ -58363,7 +58363,7 @@
     </row>
     <row r="270" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C270" s="55" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="D270" s="96"/>
       <c r="E270" s="96"/>
@@ -58561,7 +58561,7 @@
     </row>
     <row r="278" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C278" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="J278" s="99">
         <f>ASSUMPTIONS!$J$109*'MODEL&amp;SCHEDULE'!J274</f>
@@ -58597,7 +58597,7 @@
         <v>Days Sales Outstanding (DSO)</v>
       </c>
       <c r="D280" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="J280" s="125">
         <f>ASSUMPTIONS!J74</f>
@@ -58997,7 +58997,7 @@
     </row>
     <row r="308" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C308" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="J308" s="99"/>
       <c r="K308" s="99"/>
@@ -59178,7 +59178,7 @@
     </row>
     <row r="317" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C317" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="J317" s="99"/>
       <c r="K317" s="99"/>
@@ -59188,7 +59188,7 @@
     </row>
     <row r="318" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C318" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="J318" s="99">
         <f>(J282/J272)*J275</f>
@@ -59343,7 +59343,7 @@
     </row>
     <row r="324" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C324" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="J324" s="99">
         <f>J504</f>
@@ -59625,7 +59625,7 @@
     </row>
     <row r="338" spans="2:16" s="127" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C338" s="210" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D338" s="210"/>
       <c r="E338" s="210"/>
@@ -59965,7 +59965,7 @@
         <v>341</v>
       </c>
       <c r="C365" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J365" s="100">
         <f>I368</f>
@@ -59993,7 +59993,7 @@
         <v>342</v>
       </c>
       <c r="C366" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="J366" s="100">
         <f>$J$357*J346</f>
@@ -60049,7 +60049,7 @@
         <v>344</v>
       </c>
       <c r="C368" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I368">
         <f>I340</f>
@@ -60106,7 +60106,7 @@
         <v>341</v>
       </c>
       <c r="C372" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J372" s="100">
         <f>I377</f>
@@ -60242,7 +60242,7 @@
         <v>344</v>
       </c>
       <c r="C377" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I377" s="2">
         <f>I342</f>
@@ -60299,7 +60299,7 @@
         <v>341</v>
       </c>
       <c r="C381" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J381" s="100">
         <f>I384</f>
@@ -60327,7 +60327,7 @@
         <v>342</v>
       </c>
       <c r="C382" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J382" s="100">
         <f>$J$358*J346</f>
@@ -60383,7 +60383,7 @@
         <v>344</v>
       </c>
       <c r="C384" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I384" s="2">
         <f>I341</f>
@@ -60440,7 +60440,7 @@
         <v>341</v>
       </c>
       <c r="C388" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="J388" s="100">
         <f>I391</f>
@@ -60530,7 +60530,7 @@
         <v>344</v>
       </c>
       <c r="C391" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="I391">
         <f>I189</f>
@@ -60564,7 +60564,7 @@
     </row>
     <row r="395" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C395" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="J395" s="56">
         <f>$J$359*J17</f>
@@ -60842,7 +60842,7 @@
     </row>
     <row r="412" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C412" t="str">
         <f>C201</f>
@@ -60908,7 +60908,7 @@
     </row>
     <row r="415" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C415" t="str">
         <f>C224</f>
@@ -61025,7 +61025,7 @@
     </row>
     <row r="424" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C424" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="J424" s="99">
         <f>J32</f>
@@ -61057,7 +61057,7 @@
     </row>
     <row r="426" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C426" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="J426" s="99"/>
       <c r="K426" s="99"/>
@@ -61074,7 +61074,7 @@
     </row>
     <row r="428" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C428" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="J428" s="126">
         <f>J424*$J$420</f>
@@ -61515,7 +61515,7 @@
     </row>
     <row r="448" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C448" s="96" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D448" s="55"/>
       <c r="E448" s="96"/>
@@ -61813,7 +61813,7 @@
     </row>
     <row r="460" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C460" s="55" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D460" s="55"/>
       <c r="E460" s="55"/>
@@ -62119,7 +62119,7 @@
     </row>
     <row r="474" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C474" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J474" s="99"/>
       <c r="K474" s="121"/>
@@ -62133,7 +62133,7 @@
         <v>Issuance/(buyback) of common shares</v>
       </c>
       <c r="D475" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="J475" s="123">
         <f>-(J460/$J$464)</f>
@@ -62196,7 +62196,7 @@
     </row>
     <row r="478" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C478" s="96" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D478" s="110">
         <v>0.5</v>
@@ -62243,7 +62243,7 @@
     </row>
     <row r="481" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C481" s="55" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D481" s="55"/>
       <c r="E481" s="55"/>
@@ -62326,7 +62326,7 @@
     </row>
     <row r="484" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C484" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="J484" s="131">
         <f>J517/J521</f>
@@ -62379,7 +62379,7 @@
     </row>
     <row r="489" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C489" s="96" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D489" s="55"/>
       <c r="E489" s="55"/>
@@ -62410,7 +62410,7 @@
     </row>
     <row r="490" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C490" s="96" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D490" s="55"/>
       <c r="E490" s="55"/>
@@ -62482,7 +62482,7 @@
     </row>
     <row r="493" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C493" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D493" s="55"/>
       <c r="E493" s="55"/>
@@ -62498,7 +62498,7 @@
     </row>
     <row r="494" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C494" s="96" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D494" s="55"/>
       <c r="E494" s="55"/>
@@ -62529,7 +62529,7 @@
     </row>
     <row r="495" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C495" s="96" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D495" s="55"/>
       <c r="E495" s="55"/>
@@ -62641,7 +62641,7 @@
     </row>
     <row r="500" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C500" s="102" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D500" s="55"/>
       <c r="E500" s="55"/>
@@ -62657,7 +62657,7 @@
     </row>
     <row r="501" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C501" s="55" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D501" s="55"/>
       <c r="E501" s="55"/>
@@ -62673,7 +62673,7 @@
     </row>
     <row r="502" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C502" s="96" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D502" s="55"/>
       <c r="E502" s="55"/>
@@ -62704,7 +62704,7 @@
     </row>
     <row r="503" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C503" s="96" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="D503" s="55"/>
       <c r="E503" s="55"/>
@@ -62735,7 +62735,7 @@
     </row>
     <row r="504" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C504" s="55" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D504" s="55"/>
       <c r="E504" s="55"/>
@@ -62786,7 +62786,7 @@
     </row>
     <row r="509" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C509" s="102" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D509" s="55"/>
       <c r="E509" s="55"/>
@@ -62802,7 +62802,7 @@
     </row>
     <row r="510" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C510" s="55" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D510" s="55"/>
       <c r="E510" s="55"/>
@@ -62818,7 +62818,7 @@
     </row>
     <row r="511" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C511" s="96" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D511" s="55"/>
       <c r="E511" s="55"/>
@@ -62915,7 +62915,7 @@
     </row>
     <row r="515" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C515" s="102" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D515" s="55"/>
       <c r="E515" s="55"/>
@@ -62931,7 +62931,7 @@
     </row>
     <row r="516" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C516" s="96" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D516" s="55"/>
       <c r="E516" s="55"/>
@@ -62962,7 +62962,7 @@
     </row>
     <row r="517" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C517" s="96" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D517" s="55"/>
       <c r="E517" s="55"/>
@@ -62993,7 +62993,7 @@
     </row>
     <row r="518" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C518" s="96" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D518" s="55"/>
       <c r="E518" s="55"/>
@@ -63055,7 +63055,7 @@
     </row>
     <row r="520" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C520" s="96" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D520" s="55"/>
       <c r="E520" s="55"/>
@@ -63086,7 +63086,7 @@
     </row>
     <row r="521" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C521" s="96" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D521" s="55"/>
       <c r="E521" s="55"/>
@@ -63182,7 +63182,7 @@
     </row>
     <row r="527" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C527" s="96" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D527" s="55"/>
       <c r="E527" s="55"/>
@@ -63213,7 +63213,7 @@
     </row>
     <row r="528" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C528" s="96" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="D528" s="55"/>
       <c r="E528" s="55"/>
@@ -63244,7 +63244,7 @@
     </row>
     <row r="529" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C529" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="I529" s="47">
         <f>I442</f>
@@ -63273,12 +63273,12 @@
     </row>
     <row r="532" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C532" s="147" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="533" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C533" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="J533">
         <f>I536</f>
@@ -63303,7 +63303,7 @@
     </row>
     <row r="534" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C534" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="K534">
         <f>K146</f>
@@ -63324,7 +63324,7 @@
     </row>
     <row r="535" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C535" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="J535">
         <f>J465</f>
@@ -63349,7 +63349,7 @@
     </row>
     <row r="536" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C536" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="I536" s="47">
         <f>I443</f>
@@ -63378,12 +63378,12 @@
     </row>
     <row r="539" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C539" s="147" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="540" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C540" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J540" s="99">
         <f>I544</f>
@@ -63408,7 +63408,7 @@
     </row>
     <row r="541" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C541" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="J541" s="99">
         <f>I38*(1+J470)</f>
@@ -63433,7 +63433,7 @@
     </row>
     <row r="542" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C542" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="J542" s="99">
         <f>J164</f>
@@ -63465,7 +63465,7 @@
     </row>
     <row r="544" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C544" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="I544" s="47">
         <f>I450</f>
@@ -63523,7 +63523,7 @@
     </row>
     <row r="550" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C550" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E550">
         <v>50.4</v>
@@ -63603,7 +63603,7 @@
     </row>
     <row r="552" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C552" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E552" s="2">
         <f>E550+E551</f>
@@ -63685,7 +63685,7 @@
     </row>
     <row r="554" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C554" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E554" s="47">
         <f>SUM(E552:E553)</f>
@@ -63833,7 +63833,7 @@
     </row>
     <row r="560" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C560" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="E560" s="47">
         <f>SUM(E558:E559)</f>
@@ -63892,7 +63892,7 @@
     </row>
     <row r="562" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C562" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="J562" s="99"/>
       <c r="K562" s="99"/>
@@ -63902,7 +63902,7 @@
     </row>
     <row r="563" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C563" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="J563" s="99">
         <f>J757</f>
@@ -63927,7 +63927,7 @@
     </row>
     <row r="564" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C564" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="J564" s="99">
         <f>J729</f>
@@ -63952,7 +63952,7 @@
     </row>
     <row r="565" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C565" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="J565" s="99">
         <f>J572</f>
@@ -63999,12 +63999,12 @@
     </row>
     <row r="567" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C567" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="568" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C568" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="J568" s="126">
         <f>J776</f>
@@ -64029,7 +64029,7 @@
     </row>
     <row r="570" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C570" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="E570" s="2"/>
       <c r="F570" s="2"/>
@@ -64059,7 +64059,7 @@
     </row>
     <row r="571" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C571" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E571" s="2"/>
       <c r="F571" s="2"/>
@@ -64131,12 +64131,12 @@
     </row>
     <row r="574" spans="1:14" ht="21" x14ac:dyDescent="0.4">
       <c r="C574" s="54" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="575" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C575" t="str">
         <f>C208</f>
@@ -64185,7 +64185,7 @@
     </row>
     <row r="576" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C576" t="str">
         <f>C218</f>
@@ -64234,15 +64234,15 @@
     </row>
     <row r="578" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="579" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C579" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E579">
         <v>233.1</v>
@@ -64282,7 +64282,7 @@
     </row>
     <row r="580" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C580" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G580">
         <v>23.6</v>
@@ -64313,7 +64313,7 @@
     </row>
     <row r="581" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C581" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G581">
         <v>5</v>
@@ -64409,7 +64409,7 @@
     </row>
     <row r="585" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C585" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E585">
         <v>50</v>
@@ -64443,7 +64443,7 @@
     </row>
     <row r="586" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C586" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G586">
         <v>49</v>
@@ -64609,7 +64609,7 @@
     </row>
     <row r="592" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C592" s="2" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E592" s="47">
         <f t="shared" ref="E592:H592" si="291">E590-E591</f>
@@ -64754,7 +64754,7 @@
     </row>
     <row r="605" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C605" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="J605" s="82"/>
     </row>
@@ -64868,7 +64868,7 @@
         <v>Corporate bonds 4.375% repayable October 2026</v>
       </c>
       <c r="D621" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="J621" s="82">
         <f>ASSUMPTIONS!J164</f>
@@ -64881,7 +64881,7 @@
         <v>Corporate bonds 3.625% repayable May 2028</v>
       </c>
       <c r="D622" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="L622" s="82">
         <f>ASSUMPTIONS!L165</f>
@@ -64894,7 +64894,7 @@
         <v>Corporate bonds 5.0% repayable July 2031</v>
       </c>
       <c r="D623" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="624" spans="3:12" x14ac:dyDescent="0.3">
@@ -64992,7 +64992,7 @@
     </row>
     <row r="638" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C638" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D638" s="117">
         <f>SUM(D636:D637)</f>
@@ -65120,12 +65120,12 @@
     </row>
     <row r="655" spans="2:16" ht="23.4" x14ac:dyDescent="0.45">
       <c r="C655" s="63" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="656" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C656" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="J656" s="99">
         <f>J113</f>
@@ -65150,7 +65150,7 @@
     </row>
     <row r="657" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C657" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="J657" s="99">
         <f>J137</f>
@@ -65175,7 +65175,7 @@
     </row>
     <row r="658" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C658" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="J658" s="99">
         <f>J141</f>
@@ -65200,7 +65200,7 @@
     </row>
     <row r="659" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C659" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="J659" s="99">
         <f>J143</f>
@@ -65225,7 +65225,7 @@
     </row>
     <row r="660" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C660" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="J660" s="99">
         <f>J146+J147</f>
@@ -65250,7 +65250,7 @@
     </row>
     <row r="661" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C661" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="J661" s="99">
         <f>J156+J157+J158</f>
@@ -65275,7 +65275,7 @@
     </row>
     <row r="662" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C662" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="J662" s="99">
         <f>J159</f>
@@ -65300,7 +65300,7 @@
     </row>
     <row r="663" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C663" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="J663" s="99">
         <f>J162+J163+J164</f>
@@ -65325,7 +65325,7 @@
     </row>
     <row r="664" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C664" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="J664" s="126">
         <f>SUM(J656:J663)</f>
@@ -65357,7 +65357,7 @@
     </row>
     <row r="666" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C666" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="J666" s="99">
         <f>J167</f>
@@ -65382,7 +65382,7 @@
     </row>
     <row r="667" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C667" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="J667" s="126">
         <f>SUM(J664:J666)</f>
@@ -65414,7 +65414,7 @@
     </row>
     <row r="669" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C669" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="J669" s="99">
         <f>-I598</f>
@@ -65439,7 +65439,7 @@
     </row>
     <row r="670" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C670" s="2" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="J670" s="126">
         <f>SUM(J667:J669)</f>
@@ -65471,7 +65471,7 @@
     </row>
     <row r="672" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C672" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="J672" s="99">
         <f>-$I$642*J17</f>
@@ -65496,7 +65496,7 @@
     </row>
     <row r="673" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C673" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="J673" s="126">
         <f>SUM(J670:J672)</f>
@@ -65528,7 +65528,7 @@
     </row>
     <row r="675" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C675" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="J675" s="99">
         <f>I677</f>
@@ -65553,7 +65553,7 @@
     </row>
     <row r="676" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C676" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="J676" s="99">
         <f>MIN(J673,J675)*-1</f>
@@ -65578,7 +65578,7 @@
     </row>
     <row r="677" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C677" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="I677" s="47">
         <f>I580</f>
@@ -65615,7 +65615,7 @@
     </row>
     <row r="679" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C679" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D679" s="90">
         <f>D652</f>
@@ -65629,7 +65629,7 @@
     </row>
     <row r="680" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C680" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="J680" s="126">
         <f>IF(circularity=1,AVERAGE(I677:J677)*$D$679,J675*$D$679)</f>
@@ -65682,7 +65682,7 @@
     </row>
     <row r="684" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C684" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="E684" s="2"/>
       <c r="F684" s="2"/>
@@ -65712,7 +65712,7 @@
     </row>
     <row r="685" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C685" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E685" s="2"/>
       <c r="F685" s="2"/>
@@ -65741,7 +65741,7 @@
     </row>
     <row r="686" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C686" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E686" s="2"/>
       <c r="F686" s="2"/>
@@ -65784,7 +65784,7 @@
     </row>
     <row r="688" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C688" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D688" s="60"/>
       <c r="J688" s="2">
@@ -65827,12 +65827,12 @@
     </row>
     <row r="691" spans="1:16" ht="23.4" x14ac:dyDescent="0.45">
       <c r="C691" s="63" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="692" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C692" t="str">
         <f>C209</f>
@@ -65869,7 +65869,7 @@
     </row>
     <row r="693" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C693" t="str">
         <f>C219</f>
@@ -66129,7 +66129,7 @@
     </row>
     <row r="704" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C704" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="J704">
         <f>I706</f>
@@ -66154,7 +66154,7 @@
     </row>
     <row r="705" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C705" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="J705">
         <f>MIN(J704,-J698)*-1</f>
@@ -66208,7 +66208,7 @@
     </row>
     <row r="707" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C707" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D707" s="90">
         <f>D614</f>
@@ -66234,7 +66234,7 @@
     </row>
     <row r="712" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C712" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="J712">
         <f>I714</f>
@@ -66251,7 +66251,7 @@
     </row>
     <row r="713" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C713" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="J713">
         <f>MIN(J712,-J699)*-1</f>
@@ -66305,7 +66305,7 @@
     </row>
     <row r="715" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C715" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D715" s="90">
         <f>D617</f>
@@ -66333,7 +66333,7 @@
     </row>
     <row r="718" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C718" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="J718">
         <f>I720</f>
@@ -66358,7 +66358,7 @@
     </row>
     <row r="719" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C719" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="J719">
         <f>MIN(J718,-J700)*-1</f>
@@ -66412,7 +66412,7 @@
     </row>
     <row r="721" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C721" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D721" s="90">
         <f>D618</f>
@@ -66450,7 +66450,7 @@
     </row>
     <row r="724" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C724" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="I724">
         <f>I607</f>
@@ -66479,7 +66479,7 @@
     </row>
     <row r="726" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C726" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D726" s="90">
         <f>D614</f>
@@ -66496,7 +66496,7 @@
     </row>
     <row r="727" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C727" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D727" s="90">
         <f>D617</f>
@@ -66519,7 +66519,7 @@
     </row>
     <row r="728" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C728" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D728" s="90">
         <f>D618</f>
@@ -66548,7 +66548,7 @@
     </row>
     <row r="729" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C729" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="J729" s="111">
         <f>J726+J727+J728</f>
@@ -66600,7 +66600,7 @@
     </row>
     <row r="733" spans="3:14" ht="18" x14ac:dyDescent="0.35">
       <c r="C733" s="62" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="J733" s="99"/>
       <c r="K733" s="99"/>
@@ -66610,7 +66610,7 @@
     </row>
     <row r="734" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C734" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E734">
         <v>18.600000000000001</v>
@@ -66650,7 +66650,7 @@
     </row>
     <row r="735" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C735" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G735">
         <v>13.1</v>
@@ -66663,7 +66663,7 @@
     </row>
     <row r="736" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C736" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E736">
         <v>4.3</v>
@@ -66703,7 +66703,7 @@
     </row>
     <row r="737" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C737" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E737">
         <v>-1.4</v>
@@ -66743,7 +66743,7 @@
     </row>
     <row r="738" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C738" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G738">
         <v>-0.1</v>
@@ -66772,7 +66772,7 @@
     </row>
     <row r="739" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C739" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E739">
         <v>0.4</v>
@@ -66812,7 +66812,7 @@
     </row>
     <row r="740" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C740" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E740" s="47">
         <f t="shared" ref="E740:N740" si="306">SUM(E734:E739)</f>
@@ -66857,7 +66857,7 @@
     </row>
     <row r="746" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C746" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="J746" s="99"/>
       <c r="K746" s="99"/>
@@ -66867,7 +66867,7 @@
     </row>
     <row r="747" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C747" t="str">
         <f>C211</f>
@@ -66916,7 +66916,7 @@
     </row>
     <row r="748" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C748" t="str">
         <f>C221</f>
@@ -67120,7 +67120,7 @@
     </row>
     <row r="754" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C754" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="G754">
         <v>-84.7</v>
@@ -67133,7 +67133,7 @@
     </row>
     <row r="755" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C755" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E755">
         <v>-12.9</v>
@@ -67173,7 +67173,7 @@
     </row>
     <row r="756" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C756" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E756">
         <v>222.7</v>
@@ -67213,7 +67213,7 @@
     </row>
     <row r="757" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C757" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E757">
         <v>-50.4</v>
@@ -67293,7 +67293,7 @@
     </row>
     <row r="759" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C759" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E759">
         <v>0.7</v>
@@ -67328,7 +67328,7 @@
     </row>
     <row r="760" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C760" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="E760" s="47">
         <f>SUM(E752:E759)</f>
@@ -67373,7 +67373,7 @@
     </row>
     <row r="761" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C761" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D761" s="90">
         <f>J626</f>
@@ -67392,7 +67392,7 @@
     </row>
     <row r="766" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C766" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="J766" s="99">
         <f>J167</f>
@@ -67417,7 +67417,7 @@
     </row>
     <row r="767" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C767" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J767" s="99">
         <f>J664+J676+J685+J705+J713+J719</f>
@@ -67442,7 +67442,7 @@
     </row>
     <row r="768" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C768" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="J768" s="111">
         <f>J766+J767</f>
@@ -67467,7 +67467,7 @@
     </row>
     <row r="771" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C771" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E771" s="2"/>
       <c r="F771" s="2"/>
@@ -67497,7 +67497,7 @@
     </row>
     <row r="772" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C772" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E772" s="2"/>
       <c r="F772" s="2"/>
@@ -67527,7 +67527,7 @@
     </row>
     <row r="773" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C773" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="E773" s="2"/>
       <c r="F773" s="2"/>
@@ -67573,7 +67573,7 @@
     </row>
     <row r="775" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C775" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D775" s="90">
         <f>D647</f>
@@ -67592,7 +67592,7 @@
     </row>
     <row r="776" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C776" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E776" s="2"/>
       <c r="F776" s="2"/>
@@ -67629,7 +67629,7 @@
     </row>
     <row r="778" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C778" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G778">
         <f>G590-33.9</f>
@@ -67643,7 +67643,7 @@
     </row>
     <row r="779" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C779" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="G779">
         <f>33.9+G581</f>
@@ -67664,7 +67664,7 @@
     </row>
     <row r="781" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C781" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G781" s="2">
         <f>G778-G591</f>
@@ -67706,7 +67706,7 @@
     </row>
     <row r="786" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C786" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="787" spans="2:9" x14ac:dyDescent="0.3">
@@ -67737,7 +67737,7 @@
     </row>
     <row r="788" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B788" s="2" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C788" s="2"/>
     </row>
@@ -67803,7 +67803,7 @@
     </row>
     <row r="793" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B793" s="2" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="E793" s="46">
         <f>SUM(E787:E792)</f>
@@ -67863,7 +67863,7 @@
     </row>
     <row r="798" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C798" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="E798">
         <v>-1.2</v>
@@ -67883,7 +67883,7 @@
     </row>
     <row r="799" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C799" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="G799">
         <v>1.7</v>
@@ -67945,7 +67945,7 @@
     </row>
     <row r="803" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C803" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H803">
         <v>-10</v>
@@ -67956,7 +67956,7 @@
     </row>
     <row r="804" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C804" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I804">
         <v>8</v>
@@ -67989,7 +67989,7 @@
     </row>
     <row r="807" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C807" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="E807" s="2">
         <f>SUM(E794:E806)</f>
@@ -68076,49 +68076,49 @@
     </row>
     <row r="814" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C814" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E814" t="s">
         <v>1342</v>
       </c>
-      <c r="E814" t="s">
+      <c r="F814" t="s">
         <v>1343</v>
-      </c>
-      <c r="F814" t="s">
-        <v>1344</v>
       </c>
       <c r="G814" t="s">
         <v>301</v>
       </c>
       <c r="H814" t="s">
+        <v>1342</v>
+      </c>
+      <c r="I814" t="s">
         <v>1343</v>
-      </c>
-      <c r="I814" t="s">
-        <v>1344</v>
       </c>
       <c r="J814" t="s">
         <v>301</v>
       </c>
       <c r="K814" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L814" t="s">
         <v>1343</v>
-      </c>
-      <c r="L814" t="s">
-        <v>1344</v>
       </c>
       <c r="M814" t="s">
         <v>301</v>
       </c>
       <c r="N814" t="s">
+        <v>1342</v>
+      </c>
+      <c r="O814" t="s">
         <v>1343</v>
-      </c>
-      <c r="O814" t="s">
-        <v>1344</v>
       </c>
       <c r="P814" t="s">
         <v>301</v>
       </c>
       <c r="Q814" t="s">
+        <v>1342</v>
+      </c>
+      <c r="R814" t="s">
         <v>1343</v>
-      </c>
-      <c r="R814" t="s">
-        <v>1344</v>
       </c>
       <c r="S814" t="s">
         <v>301</v>
@@ -68304,7 +68304,7 @@
     </row>
     <row r="819" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C819" s="2" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="821" spans="3:19" x14ac:dyDescent="0.3">
@@ -68368,7 +68368,7 @@
       <c r="A1" s="16"/>
       <c r="B1" s="16"/>
       <c r="C1" s="201" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
@@ -68407,7 +68407,7 @@
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="18" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
@@ -68579,13 +68579,13 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="C7" s="2" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>1356</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>1357</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
@@ -68594,10 +68594,10 @@
         <v>2027 ONLY using the Whole Revenue</v>
       </c>
       <c r="J8" s="200" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="R8" s="200" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="21" x14ac:dyDescent="0.4">
@@ -68613,7 +68613,7 @@
         <v>EBIAT/NOPAT</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>303</v>
@@ -68621,7 +68621,7 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="I11" s="2" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="Q11">
         <f>I96*(1+J97)*(J88*(1-J90))</f>
@@ -69394,30 +69394,30 @@
     <row r="51" spans="2:9" s="127" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C53" s="2" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>1374</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>1370</v>
-      </c>
       <c r="G53" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>1377</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>1378</v>
-      </c>
       <c r="I53" s="2" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
@@ -69486,7 +69486,7 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="D58" s="90">
         <f>(1-D$56-$J$99)</f>
@@ -69503,7 +69503,7 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C59" s="2" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="E59">
         <f>$I$96*(1+E54)*($E$55*(1-E57))</f>
@@ -69512,7 +69512,7 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D60" s="99">
         <f>$I$96*(1+D$54)*($E$55*(1-$E$57))</f>
@@ -69635,7 +69635,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66" s="2" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D66" s="99"/>
       <c r="E66" s="99"/>
@@ -69727,7 +69727,7 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72" s="2" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
@@ -69815,7 +69815,7 @@
     </row>
     <row r="84" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B84" s="2" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="85" spans="2:26" x14ac:dyDescent="0.3">
@@ -69824,7 +69824,7 @@
         <v>Online UK</v>
       </c>
       <c r="D85" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I85">
         <f>'MODEL&amp;SCHEDULE'!I9</f>
@@ -69853,7 +69853,7 @@
     </row>
     <row r="86" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B86" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="87" spans="2:26" x14ac:dyDescent="0.3">
@@ -69953,7 +69953,7 @@
     </row>
     <row r="91" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B91" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="G91" s="60"/>
     </row>
@@ -69994,7 +69994,7 @@
     </row>
     <row r="94" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="G94" s="60"/>
       <c r="J94" s="2"/>
@@ -70005,7 +70005,7 @@
     </row>
     <row r="95" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B95" s="2" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="G95" s="60"/>
       <c r="J95" s="2"/>
@@ -70078,7 +70078,7 @@
     </row>
     <row r="98" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C98" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G98" s="60"/>
       <c r="J98" s="115">
@@ -70092,7 +70092,7 @@
     </row>
     <row r="99" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C99" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G99" s="60"/>
       <c r="J99" s="61">
